--- a/presupuesto/MathBot_Presupuesto_SCARA.xlsx
+++ b/presupuesto/MathBot_Presupuesto_SCARA.xlsx
@@ -38,7 +38,7 @@
     <definedName name="RendimientoGH">Supuestos!$C$17</definedName>
     <definedName name="TasaVentasEEUU">Supuestos!$C$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3843,8 +3843,10 @@
       <c r="Z5" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="AA5" s="28" t="s">
-        <v>95</v>
+      <c r="AA5" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTM usa 400 mm. Con el cabezal de disco v3 bastan 250 mm (NEMA estándar en J2) o 240 mm (NEMA corto): comprar 300 y cortar.</t>
+        </is>
       </c>
       <c r="AB5" s="26">
         <f t="shared" ref="AB5:AB49" si="6">IF(AND(S5="Amazon",ISNUMBER(M5),W5&gt;0),ROUNDUP(G5/N5,0)*M5,0)</f>
@@ -4033,8 +4035,10 @@
       <c r="Z7" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="AA7" s="28" t="s">
-        <v>108</v>
+      <c r="AA7" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTM lo corta a 380 mm para varillas de 400; con varillas de 250 mm cortar a ≈230 mm. El paquete trae 2.</t>
+        </is>
       </c>
       <c r="AB7" s="26">
         <f t="shared" si="6"/>
@@ -5073,8 +5077,10 @@
       <c r="Z18" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="AA18" s="28" t="s">
-        <v>173</v>
+      <c r="AA18" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prestados. Si usan el NEMA corto también en J2 (varillas de 240 mm), bajar a 2 y subir ELE-02 a 2. Confirmar que trae cable.</t>
+        </is>
       </c>
       <c r="AB18" s="26">
         <f t="shared" si="6"/>
@@ -6281,8 +6287,10 @@
       <c r="C32" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>256</v>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ø15–16 × 30 mm, alambre 0.5–0.6 (Ø int. ≥ 13.5, sólido ≤ 6 mm)</t>
+        </is>
       </c>
       <c r="E32" s="22" t="s">
         <v>257</v>
@@ -6355,8 +6363,10 @@
       <c r="Z32" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="AA32" s="28" t="s">
-        <v>260</v>
+      <c r="AA32" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Va alrededor del plumón (Ø12): el de Ø10–12 × 20 no entra ni da 18 mm de levante. Ver Cabezal disco/README.md.</t>
+        </is>
       </c>
       <c r="AB32" s="26">
         <f t="shared" si="6"/>
@@ -6374,14 +6384,20 @@
       <c r="B33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>264</v>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tornillería del cabezal A v3</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 × M4×35 + tuerca + arandela + fijador de rosca; M3: 4×10, 1×12, 3×20, 1×35, 3×16 avellanados + 11 tuercas</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placa + separador al J3 Coupler y montaje de las herramientas</t>
+        </is>
       </c>
       <c r="F33" s="21" t="s">
         <v>192</v>
@@ -6443,8 +6459,10 @@
       </c>
       <c r="Y33" s="23"/>
       <c r="Z33" s="21"/>
-      <c r="AA33" s="28" t="s">
-        <v>266</v>
+      <c r="AA33" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El separador del electroimán ahora es impreso (hoja Impresión 3D). Lista por pieza en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/README.md.</t>
+        </is>
       </c>
       <c r="AB33" s="26">
         <f t="shared" si="6"/>
@@ -16233,8 +16251,10 @@
       <c r="A37" s="37">
         <v>25</v>
       </c>
-      <c r="B37" s="37" t="s">
-        <v>413</v>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placa trébol del cabezal A v3 (6 mm, PETG)</t>
+        </is>
       </c>
       <c r="C37" s="37" t="s">
         <v>28</v>
@@ -16242,21 +16262,23 @@
       <c r="D37" s="37">
         <v>1</v>
       </c>
-      <c r="E37" s="50"/>
+      <c r="E37" s="50">
+        <v>35.8</v>
+      </c>
       <c r="F37" s="53">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="G37" s="50">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="H37" s="50">
         <f t="shared" si="1"/>
-        <v>2.5641025641025643</v>
+        <v>2.6923076923076925</v>
       </c>
       <c r="I37" s="50">
         <f t="shared" si="2"/>
-        <v>2.5641025641025643</v>
+        <v>2.6923076923076925</v>
       </c>
       <c r="J37" s="36" t="s">
         <v>382</v>
@@ -16266,16 +16288,20 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M37" s="52" t="s">
-        <v>414</v>
+      <c r="M37" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STL en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/STL/02_placa_trebol.stl · boca abajo, sin soportes</t>
+        </is>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>26</v>
       </c>
-      <c r="B38" s="37" t="s">
-        <v>415</v>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separador de brida 14 mm (PETG)</t>
+        </is>
       </c>
       <c r="C38" s="37" t="s">
         <v>28</v>
@@ -16283,21 +16309,23 @@
       <c r="D38" s="37">
         <v>1</v>
       </c>
-      <c r="E38" s="50"/>
+      <c r="E38" s="50">
+        <v>9.7</v>
+      </c>
       <c r="F38" s="53">
-        <v>8</v>
+        <v>12.4</v>
       </c>
       <c r="G38" s="50">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12.4</v>
       </c>
       <c r="H38" s="50">
         <f t="shared" si="1"/>
-        <v>0.68376068376068377</v>
+        <v>1.0598290598290598</v>
       </c>
       <c r="I38" s="50">
         <f t="shared" si="2"/>
-        <v>0.68376068376068377</v>
+        <v>1.0598290598290598</v>
       </c>
       <c r="J38" s="36" t="s">
         <v>382</v>
@@ -16307,16 +16335,20 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M38" s="52" t="s">
-        <v>414</v>
+      <c r="M38" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STL en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/STL/01_separador_brida.stl · baja la placa 14 mm para no chocar con la cubierta del brazo 2</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>27</v>
       </c>
-      <c r="B39" s="37" t="s">
-        <v>416</v>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soporte plumón/servo + puente + collar (PETG, 3 piezas)</t>
+        </is>
       </c>
       <c r="C39" s="37" t="s">
         <v>28</v>
@@ -16324,21 +16356,23 @@
       <c r="D39" s="37">
         <v>1</v>
       </c>
-      <c r="E39" s="50"/>
+      <c r="E39" s="50">
+        <v>9.7</v>
+      </c>
       <c r="F39" s="53">
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="G39" s="50">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="H39" s="50">
         <f t="shared" si="1"/>
-        <v>0.42735042735042739</v>
+        <v>1.0085470085470087</v>
       </c>
       <c r="I39" s="50">
         <f t="shared" si="2"/>
-        <v>0.42735042735042739</v>
+        <v>1.0085470085470087</v>
       </c>
       <c r="J39" s="36" t="s">
         <v>382</v>
@@ -16348,16 +16382,20 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="52" t="s">
-        <v>414</v>
+      <c r="M39" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STL en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/STL/03, 04 y 05 · gramos de las tres piezas</t>
+        </is>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>28</v>
       </c>
-      <c r="B40" s="37" t="s">
-        <v>417</v>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separador del electroimán con copa (PLA+)</t>
+        </is>
       </c>
       <c r="C40" s="37" t="s">
         <v>28</v>
@@ -16365,21 +16403,23 @@
       <c r="D40" s="37">
         <v>1</v>
       </c>
-      <c r="E40" s="50"/>
+      <c r="E40" s="50">
+        <v>6.5</v>
+      </c>
       <c r="F40" s="53">
-        <v>3</v>
+        <v>6.0</v>
       </c>
       <c r="G40" s="50">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6.0</v>
       </c>
       <c r="H40" s="50">
         <f t="shared" si="1"/>
-        <v>0.25641025641025644</v>
+        <v>0.5128205128205129</v>
       </c>
       <c r="I40" s="50">
         <f t="shared" si="2"/>
-        <v>0.25641025641025644</v>
+        <v>0.5128205128205129</v>
       </c>
       <c r="J40" s="36" t="s">
         <v>382</v>
@@ -16389,16 +16429,20 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M40" s="52" t="s">
-        <v>414</v>
+      <c r="M40" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STL en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/STL/06_separador_electroiman.stl · reemplaza el separador M4 × 25</t>
+        </is>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>29</v>
       </c>
-      <c r="B41" s="37" t="s">
-        <v>418</v>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abrazadera M12 del sensor (PLA+)</t>
+        </is>
       </c>
       <c r="C41" s="37" t="s">
         <v>28</v>
@@ -16406,21 +16450,23 @@
       <c r="D41" s="37">
         <v>1</v>
       </c>
-      <c r="E41" s="50"/>
+      <c r="E41" s="50">
+        <v>6.9</v>
+      </c>
       <c r="F41" s="53">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="G41" s="50">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="H41" s="50">
         <f t="shared" si="1"/>
-        <v>0.34188034188034189</v>
+        <v>0.5213675213675214</v>
       </c>
       <c r="I41" s="50">
         <f t="shared" si="2"/>
-        <v>0.34188034188034189</v>
+        <v>0.5213675213675214</v>
       </c>
       <c r="J41" s="36" t="s">
         <v>382</v>
@@ -16430,8 +16476,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M41" s="52" t="s">
-        <v>414</v>
+      <c r="M41" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STL en BRAZO SCARA/DISEÑO FINAL/Cabezal disco/STL/07_abrazadera_sensor_M12.stl</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">

--- a/presupuesto/MathBot_Presupuesto_SCARA.xlsx
+++ b/presupuesto/MathBot_Presupuesto_SCARA.xlsx
@@ -30,7 +30,7 @@
     <definedName name="RendimientoGH">Supuestos!$C$17</definedName>
     <definedName name="GramosRollo">Supuestos!$C$18</definedName>
     <definedName name="Miembros">Supuestos!$B$23:$B$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lista de materiales'!$A$4:$AC$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lista de materiales'!$A$4:$AC$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -941,7 +941,7 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="8">
-        <f>SUM('Lista de materiales'!$W$5:$W$51)</f>
+        <f>SUM('Lista de materiales'!$W$5:$W$54)</f>
         <v/>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="8">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="8">
-        <f>SUMIFS('Lista de materiales'!$AC$5:$AC$51,'Lista de materiales'!$U$5:$U$51,"Por comprar")+SUMIFS('Lista de materiales'!$AC$5:$AC$51,'Lista de materiales'!$U$5:$U$51,"Cotizado")</f>
+        <f>SUMIFS('Lista de materiales'!$AC$5:$AC$54,'Lista de materiales'!$U$5:$U$54,"Por comprar")+SUMIFS('Lista de materiales'!$AC$5:$AC$54,'Lista de materiales'!$U$5:$U$54,"Cotizado")</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1172,23 +1172,23 @@
         </is>
       </c>
       <c r="B20" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A20,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A20,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C20" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A20,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A20,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D20" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A20)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A20)</f>
         <v/>
       </c>
       <c r="E20" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A20)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A20)</f>
         <v/>
       </c>
       <c r="F20" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A20)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A20)</f>
         <v/>
       </c>
       <c r="G20" s="12">
@@ -1204,23 +1204,23 @@
         </is>
       </c>
       <c r="B21" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A21,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A21,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C21" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A21,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A21,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D21" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A21)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A21)</f>
         <v/>
       </c>
       <c r="E21" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A21)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A21)</f>
         <v/>
       </c>
       <c r="F21" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A21)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A21)</f>
         <v/>
       </c>
       <c r="G21" s="12">
@@ -1236,23 +1236,23 @@
         </is>
       </c>
       <c r="B22" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A22,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A22,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C22" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A22,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A22,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D22" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A22)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A22)</f>
         <v/>
       </c>
       <c r="E22" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A22)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A22)</f>
         <v/>
       </c>
       <c r="F22" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A22)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A22)</f>
         <v/>
       </c>
       <c r="G22" s="12">
@@ -1268,23 +1268,23 @@
         </is>
       </c>
       <c r="B23" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A23,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A23,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A23,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A23,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A23)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A23)</f>
         <v/>
       </c>
       <c r="E23" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A23)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A23)</f>
         <v/>
       </c>
       <c r="F23" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A23)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A23)</f>
         <v/>
       </c>
       <c r="G23" s="12">
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="B24" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A24,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A24,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C24" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A24,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A24,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D24" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A24)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A24)</f>
         <v/>
       </c>
       <c r="E24" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A24)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A24)</f>
         <v/>
       </c>
       <c r="F24" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A24)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A24)</f>
         <v/>
       </c>
       <c r="G24" s="12">
@@ -1332,23 +1332,23 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A25,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A25,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C25" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A25,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A25,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A25)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A25)</f>
         <v/>
       </c>
       <c r="E25" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A25)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A25)</f>
         <v/>
       </c>
       <c r="F25" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A25)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A25)</f>
         <v/>
       </c>
       <c r="G25" s="12">
@@ -1364,23 +1364,23 @@
         </is>
       </c>
       <c r="B26" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A26,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A26,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C26" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A26,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A26,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D26" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A26)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A26)</f>
         <v/>
       </c>
       <c r="E26" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A26)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A26)</f>
         <v/>
       </c>
       <c r="F26" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A26)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A26)</f>
         <v/>
       </c>
       <c r="G26" s="12">
@@ -1396,23 +1396,23 @@
         </is>
       </c>
       <c r="B27" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A27,'Lista de materiales'!$U$5:$U$51,"&lt;&gt;No comprar")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A27,'Lista de materiales'!$U$5:$U$54,"&lt;&gt;No comprar")</f>
         <v/>
       </c>
       <c r="C27" s="11">
-        <f>SUMIFS('Lista de materiales'!$T$5:$T$51,'Lista de materiales'!$B$5:$B$51,A27,'Lista de materiales'!$U$5:$U$51,"Ya lo tenemos")</f>
+        <f>SUMIFS('Lista de materiales'!$T$5:$T$54,'Lista de materiales'!$B$5:$B$54,A27,'Lista de materiales'!$U$5:$U$54,"Ya lo tenemos")</f>
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>SUMIFS('Lista de materiales'!$V$5:$V$51,'Lista de materiales'!$B$5:$B$51,A27)</f>
+        <f>SUMIFS('Lista de materiales'!$V$5:$V$54,'Lista de materiales'!$B$5:$B$54,A27)</f>
         <v/>
       </c>
       <c r="E27" s="11">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$B$5:$B$51,A27)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$B$5:$B$54,A27)</f>
         <v/>
       </c>
       <c r="F27" s="11">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$B$5:$B$51,A27)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$B$5:$B$54,A27)</f>
         <v/>
       </c>
       <c r="G27" s="12">
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="B32" s="15">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$S$5:$S$51,A32)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$S$5:$S$54,A32)</f>
         <v/>
       </c>
       <c r="C32" s="15">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$S$5:$S$51,A32)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$S$5:$S$54,A32)</f>
         <v/>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="F32" s="15">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$H$5:$H$51,E32)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$H$5:$H$54,E32)</f>
         <v/>
       </c>
       <c r="G32" s="15">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$H$5:$H$51,E32)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$H$5:$H$54,E32)</f>
         <v/>
       </c>
       <c r="H32" s="2" t="n"/>
@@ -1552,11 +1552,11 @@
         </is>
       </c>
       <c r="B33" s="15">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$S$5:$S$51,A33)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$S$5:$S$54,A33)</f>
         <v/>
       </c>
       <c r="C33" s="15">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$S$5:$S$51,A33)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$S$5:$S$54,A33)</f>
         <v/>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1566,11 +1566,11 @@
         </is>
       </c>
       <c r="F33" s="15">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$H$5:$H$51,E33)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$H$5:$H$54,E33)</f>
         <v/>
       </c>
       <c r="G33" s="15">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$H$5:$H$51,E33)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$H$5:$H$54,E33)</f>
         <v/>
       </c>
       <c r="H33" s="2" t="n"/>
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="F34" s="15">
-        <f>SUMIFS('Lista de materiales'!$W$5:$W$51,'Lista de materiales'!$H$5:$H$51,E34)</f>
+        <f>SUMIFS('Lista de materiales'!$W$5:$W$54,'Lista de materiales'!$H$5:$H$54,E34)</f>
         <v/>
       </c>
       <c r="G34" s="15">
-        <f>SUMIFS('Lista de materiales'!$X$5:$X$51,'Lista de materiales'!$H$5:$H$51,E34)</f>
+        <f>SUMIFS('Lista de materiales'!$X$5:$X$54,'Lista de materiales'!$H$5:$H$54,E34)</f>
         <v/>
       </c>
       <c r="H34" s="2" t="n"/>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="16">
-        <f>SUM('Lista de materiales'!$AB$5:$AB$51)</f>
+        <f>SUM('Lista de materiales'!$AB$5:$AB$54)</f>
         <v/>
       </c>
       <c r="D35" s="2" t="n"/>
@@ -1949,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Arduino UNO R3 (compatible)</t>
+          <t>Arduino MEGA 2560 R3 (compatible)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>ATmega328P</t>
+          <t>ATmega2560</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>HTM</t>
+          <t>MathBot</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
@@ -4292,28 +4292,20 @@
       </c>
       <c r="I22" s="24" t="inlineStr">
         <is>
-          <t>Steren (ARD-010)</t>
-        </is>
-      </c>
-      <c r="J22" s="26" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="K22" s="25" t="n">
-        <v>1</v>
-      </c>
+          <t>Electrónica 2001 / Casa Rivas</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="n"/>
+      <c r="K22" s="25" t="n"/>
       <c r="L22" s="24" t="inlineStr">
         <is>
-          <t>Verificado en línea 06-oct-2026</t>
-        </is>
-      </c>
-      <c r="M22" s="26" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>1</v>
-      </c>
+          <t>Cotizar</t>
+        </is>
+      </c>
+      <c r="M22" s="26" t="n"/>
+      <c r="N22" s="25" t="n"/>
       <c r="O22" s="27" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="P22" s="28">
         <f>IF(J22="","",ROUNDUP(G22/K22,0)*J22*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I22)),DescCasaRivas,0)))</f>
@@ -4356,12 +4348,12 @@
       <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="29" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0B6VV7MS7</t>
+          <t>https://www.amazon.com/s?k=Arduino+Mega+2560+R3</t>
         </is>
       </c>
       <c r="AA22" s="30" t="inlineStr">
         <is>
-          <t>Prestado. Steren la vende como 'Placa de desarrollo ARD-010': confirmar en tienda que sea compatible con UNO.</t>
+          <t>Prestado: confirmar que sea un MEGA 2560 (un UNO no tiene los pines del cabezal). El firmware (firmware/mathbot_mega) usa pines que el UNO no tiene: D22 sensor, D24 electroimán, D44 servo. La CNC Shield V3 encaja igual que sobre el UNO.</t>
         </is>
       </c>
       <c r="AB22" s="28">
@@ -5656,7 +5648,7 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Encender el electroimán desde A1</t>
+          <t>Encender el electroimán desde D24</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
@@ -5888,7 +5880,7 @@
       <c r="D36" s="24" t="inlineStr"/>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Llevar la señal de 12 V del sensor a A2</t>
+          <t>Llevar la señal de 12 V del sensor a D22</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
@@ -6320,32 +6312,28 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>TOR-01</t>
+          <t>MB-07</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Tornillería</t>
+          <t>Electrónica MathBot</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Surtido de tornillos Allen M3/M4/M5 + tuercas</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>≈ 20 M3 × 8–16, 40–50 M4 × 16–30 y sus tuercas</t>
-        </is>
-      </c>
+          <t>Pulsador NA (START) + hongo de paro NC</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr"/>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>Tornillos chicos del brazo: motores, abrazaderas de varilla, tapas, placas Z y acoples</t>
+          <t>Iniciar la misión (D26) y PARO (D28)</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>HTM</t>
+          <t>MathBot</t>
         </is>
       </c>
       <c r="G40" s="25" t="n">
@@ -6358,29 +6346,19 @@
       </c>
       <c r="I40" s="24" t="inlineStr">
         <is>
-          <t>Vidrí / Freund (por pieza)</t>
-        </is>
-      </c>
-      <c r="J40" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="K40" s="25" t="n">
-        <v>1</v>
-      </c>
+          <t>Casa Rivas / Steren</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="25" t="n"/>
       <c r="L40" s="24" t="inlineStr">
         <is>
-          <t>Estimado</t>
-        </is>
-      </c>
-      <c r="M40" s="26" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="N40" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="27" t="n">
-        <v>2.5</v>
-      </c>
+          <t>Cotizar</t>
+        </is>
+      </c>
+      <c r="M40" s="26" t="n"/>
+      <c r="N40" s="25" t="n"/>
+      <c r="O40" s="27" t="n"/>
       <c r="P40" s="28">
         <f>IF(J40="","",ROUNDUP(G40/K40,0)*J40*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I40)),DescCasaRivas,0)))</f>
         <v/>
@@ -6420,14 +6398,10 @@
         <v/>
       </c>
       <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="29" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0FG2964F5</t>
-        </is>
-      </c>
+      <c r="Z40" s="23" t="n"/>
       <c r="AA40" s="30" t="inlineStr">
         <is>
-          <t>El artículo trae la lista en una imagen y el CAD no los modela; cantidades estimadas por los agujeros del CAD (Ø3.2 = M3, Ø4.1 = M4): 16 M3 × 8–12 (4 por NEMA), 4 M3 × 16 (tuerca del husillo T8), 16 M4 × 20 (8 abrazaderas de varilla) y 20–30 M4 × 16–30 (tapas, placas Z, polea de J3). El surtido de Amazon cubre todo pero pesa 2.5 lb.</t>
+          <t>El PARO solo es software (ver firmware/README.md).</t>
         </is>
       </c>
       <c r="AB40" s="28">
@@ -6442,56 +6416,52 @@
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>TOR-02</t>
+          <t>MB-08</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Tornillería</t>
+          <t>Electrónica MathBot</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Perno M4 × 60 + tuerca de seguridad</t>
+          <t>3 LED (verde, amarillo, rojo) + buzzer + resistencias</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>DIN 912, tuerca con nylon</t>
+          <t>220 Ω para los LED; 10 kΩ / 3.3 kΩ para el divisor de 12 V</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Unir la polea de 110 dientes con el acople J1</t>
+          <t>Estado (D30–D34), aviso (D36) y monitor de 12 V (A8)</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>HTM</t>
+          <t>MathBot</t>
         </is>
       </c>
       <c r="G41" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Recomendado</t>
         </is>
       </c>
       <c r="I41" s="24" t="inlineStr">
         <is>
-          <t>Vidrí</t>
-        </is>
-      </c>
-      <c r="J41" s="26" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K41" s="25" t="n">
-        <v>1</v>
-      </c>
+          <t>Casa Rivas</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="25" t="n"/>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>Estimado</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="M41" s="26" t="n"/>
@@ -6537,11 +6507,7 @@
       </c>
       <c r="Y41" s="25" t="n"/>
       <c r="Z41" s="23" t="n"/>
-      <c r="AA41" s="30" t="inlineStr">
-        <is>
-          <t>Medida del CAD (M4 60mm - Bolts en J1). El texto del artículo decía M4 × 55.</t>
-        </is>
-      </c>
+      <c r="AA41" s="30" t="inlineStr"/>
       <c r="AB41" s="28">
         <f>IF(AND(S41="Amazon",ISNUMBER(M41),W41&gt;0),ROUNDUP(G41/N41,0)*M41,0)</f>
         <v/>
@@ -6554,7 +6520,7 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>TOR-03</t>
+          <t>TOR-01</t>
         </is>
       </c>
       <c r="B42" s="23" t="inlineStr">
@@ -6564,17 +6530,17 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Perno M4 × 50 + tuerca de seguridad</t>
+          <t>Surtido de tornillos Allen M3/M4/M5 + tuercas</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>DIN 912, tuerca con nylon</t>
+          <t>≈ 20 M3 × 8–16, 45–55 M4 × 16–30 y sus tuercas</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>Unir la polea de 92 dientes con el acople J2</t>
+          <t>Tornillos chicos del brazo: motores, abrazaderas de varilla, tapas, placas Z y acoples</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
@@ -6583,7 +6549,7 @@
         </is>
       </c>
       <c r="G42" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" s="23" t="inlineStr">
         <is>
@@ -6592,11 +6558,11 @@
       </c>
       <c r="I42" s="24" t="inlineStr">
         <is>
-          <t>Vidrí</t>
+          <t>Vidrí / Freund (por pieza)</t>
         </is>
       </c>
       <c r="J42" s="26" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="K42" s="25" t="n">
         <v>1</v>
@@ -6606,9 +6572,15 @@
           <t>Estimado</t>
         </is>
       </c>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="25" t="n"/>
-      <c r="O42" s="27" t="n"/>
+      <c r="M42" s="26" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="N42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="27" t="n">
+        <v>2.5</v>
+      </c>
       <c r="P42" s="28">
         <f>IF(J42="","",ROUNDUP(G42/K42,0)*J42*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I42)),DescCasaRivas,0)))</f>
         <v/>
@@ -6648,10 +6620,14 @@
         <v/>
       </c>
       <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="23" t="n"/>
+      <c r="Z42" s="29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B0FG2964F5</t>
+        </is>
+      </c>
       <c r="AA42" s="30" t="inlineStr">
         <is>
-          <t>Medida del CAD (M4 50mm - Bolts en J2).</t>
+          <t>El artículo trae la lista en una imagen y el CAD no los modela; cantidades estimadas por los agujeros del CAD (Ø3.2 = M3, Ø4.1 = M4): 16 M3 × 8–12 (4 por NEMA), 4 M3 × 16 (tuerca del husillo T8), 16 M4 × 20 (8 abrazaderas de varilla), 6 M4 × 20 (J2 Coupler → brazo 2) y 20–30 M4 × 16–30 (tapas, placas Z, polea de J3). El surtido de Amazon cubre todo pero pesa 2.5 lb.</t>
         </is>
       </c>
       <c r="AB42" s="28">
@@ -6666,7 +6642,7 @@
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>TOR-04</t>
+          <t>TOR-02</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
@@ -6676,13 +6652,17 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Perno M8 × 45 + arandela + tuerca de seguridad</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr"/>
+          <t>Perno M4 × 60 + tuerca de seguridad</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>DIN 912, tuerca con nylon</t>
+        </is>
+      </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Eje de las poleas intermedias de J1 y J2 (1 c/u)</t>
+          <t>Unir la polea de 110 dientes con el acople J1</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
@@ -6691,7 +6671,7 @@
         </is>
       </c>
       <c r="G43" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
@@ -6704,7 +6684,7 @@
         </is>
       </c>
       <c r="J43" s="26" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="K43" s="25" t="n">
         <v>1</v>
@@ -6757,7 +6737,11 @@
       </c>
       <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="23" t="n"/>
-      <c r="AA43" s="30" t="inlineStr"/>
+      <c r="AA43" s="30" t="inlineStr">
+        <is>
+          <t>Medida del CAD (M4 60mm - Bolts en J1). El texto del artículo decía M4 × 55.</t>
+        </is>
+      </c>
       <c r="AB43" s="28">
         <f>IF(AND(S43="Amazon",ISNUMBER(M43),W43&gt;0),ROUNDUP(G43/N43,0)*M43,0)</f>
         <v/>
@@ -6770,7 +6754,7 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>TOR-05</t>
+          <t>TOR-03</t>
         </is>
       </c>
       <c r="B44" s="23" t="inlineStr">
@@ -6780,17 +6764,17 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Perno M5 × 35 + tuercas</t>
+          <t>Perno M4 × 50 + tuerca de seguridad</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>2 tuercas por perno</t>
+          <t>DIN 912, tuerca con nylon</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>Tensores de correa</t>
+          <t>Unir la polea de 92 dientes con el acople J2</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
@@ -6803,7 +6787,7 @@
       </c>
       <c r="H44" s="23" t="inlineStr">
         <is>
-          <t>Recomendado</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="I44" s="24" t="inlineStr">
@@ -6812,7 +6796,7 @@
         </is>
       </c>
       <c r="J44" s="26" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K44" s="25" t="n">
         <v>1</v>
@@ -6865,7 +6849,11 @@
       </c>
       <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="23" t="n"/>
-      <c r="AA44" s="30" t="inlineStr"/>
+      <c r="AA44" s="30" t="inlineStr">
+        <is>
+          <t>Medida del CAD (M4 50mm - Bolts en J2).</t>
+        </is>
+      </c>
       <c r="AB44" s="28">
         <f>IF(AND(S44="Amazon",ISNUMBER(M44),W44&gt;0),ROUNDUP(G44/N44,0)*M44,0)</f>
         <v/>
@@ -6878,7 +6866,7 @@
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>TOR-06</t>
+          <t>TOR-04</t>
         </is>
       </c>
       <c r="B45" s="23" t="inlineStr">
@@ -6888,17 +6876,13 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>Tornillo M4 + tuerca</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>≈ M4 × 40: grosor de la base + 20 mm de madera</t>
-        </is>
-      </c>
+          <t>Perno M8 × 45 + arandela + tuerca de seguridad</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr"/>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>Fijar la base a la madera (12 agujeros)</t>
+          <t>Eje de las poleas intermedias de J1 y J2 (1 c/u)</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
@@ -6907,11 +6891,11 @@
         </is>
       </c>
       <c r="G45" s="25" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t>Recomendado</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="I45" s="24" t="inlineStr">
@@ -6920,7 +6904,7 @@
         </is>
       </c>
       <c r="J45" s="26" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="K45" s="25" t="n">
         <v>1</v>
@@ -6973,11 +6957,7 @@
       </c>
       <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="23" t="n"/>
-      <c r="AA45" s="30" t="inlineStr">
-        <is>
-          <t>Midan la base antes de comprar el largo.</t>
-        </is>
-      </c>
+      <c r="AA45" s="30" t="inlineStr"/>
       <c r="AB45" s="28">
         <f>IF(AND(S45="Amazon",ISNUMBER(M45),W45&gt;0),ROUNDUP(G45/N45,0)*M45,0)</f>
         <v/>
@@ -6990,7 +6970,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>TOR-07</t>
+          <t>TOR-05</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
@@ -7000,17 +6980,17 @@
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>Tornillo M2 × 10 + tuerca</t>
+          <t>Perno M5 × 35 + tuercas</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>O autorroscante para plástico</t>
+          <t>2 tuercas por perno</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>Finales de carrera (2 por switch)</t>
+          <t>Tensores de correa</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
@@ -7019,20 +6999,20 @@
         </is>
       </c>
       <c r="G46" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H46" s="23" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Recomendado</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>Vidrí / Casa Rivas</t>
+          <t>Vidrí</t>
         </is>
       </c>
       <c r="J46" s="26" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="K46" s="25" t="n">
         <v>1</v>
@@ -7085,11 +7065,7 @@
       </c>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="23" t="n"/>
-      <c r="AA46" s="30" t="inlineStr">
-        <is>
-          <t>Si los finales de carrera traen tornillos, no hace falta.</t>
-        </is>
-      </c>
+      <c r="AA46" s="30" t="inlineStr"/>
       <c r="AB46" s="28">
         <f>IF(AND(S46="Amazon",ISNUMBER(M46),W46&gt;0),ROUNDUP(G46/N46,0)*M46,0)</f>
         <v/>
@@ -7102,27 +7078,27 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>VAR-01</t>
+          <t>TOR-06</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Impresión y varios</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>Filamento PLA+ 1.75 mm</t>
+          <t>Tornillo M4 + tuerca</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>Rollo de 1 kg</t>
+          <t>≈ M4 × 40: grosor de la base + 20 mm de madera</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Todas las piezas impresas (ver hoja Impresión 3D)</t>
+          <t>Fijar la base a la madera (12 agujeros)</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
@@ -7130,40 +7106,33 @@
           <t>HTM</t>
         </is>
       </c>
-      <c r="G47" s="31">
-        <f>'Impresión 3D'!$B$6</f>
-        <v/>
+      <c r="G47" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Recomendado</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>El Changarro (PLA 1 kg)</t>
+          <t>Vidrí</t>
         </is>
       </c>
       <c r="J47" s="26" t="n">
-        <v>27.99</v>
+        <v>0.12</v>
       </c>
       <c r="K47" s="25" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="24" t="inlineStr">
         <is>
-          <t>Indexado en buscador (oferta)</t>
-        </is>
-      </c>
-      <c r="M47" s="26" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="N47" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" s="27" t="n">
-        <v>2.9</v>
-      </c>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="n"/>
+      <c r="N47" s="25" t="n"/>
+      <c r="O47" s="27" t="n"/>
       <c r="P47" s="28">
         <f>IF(J47="","",ROUNDUP(G47/K47,0)*J47*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I47)),DescCasaRivas,0)))</f>
         <v/>
@@ -7178,7 +7147,7 @@
       </c>
       <c r="S47" s="25" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="T47" s="28">
@@ -7187,7 +7156,7 @@
       </c>
       <c r="U47" s="25" t="inlineStr">
         <is>
-          <t>Ya lo tenemos</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="V47" s="28">
@@ -7203,14 +7172,10 @@
         <v/>
       </c>
       <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="29" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B07XG3RM58</t>
-        </is>
-      </c>
+      <c r="Z47" s="23" t="n"/>
       <c r="AA47" s="30" t="inlineStr">
         <is>
-          <t>Impresión gratuita: todas las piezas impresas quedan sin costo. Avalon Tech publicaba USD 30, pero cerró su tienda en línea en jul-2026: preguntar por WhatsApp. Si la universidad imprime, poner 'Ya lo tenemos'.</t>
+          <t>Midan la base antes de comprar el largo.</t>
         </is>
       </c>
       <c r="AB47" s="28">
@@ -7225,27 +7190,27 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>VAR-02</t>
+          <t>TOR-07</t>
         </is>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Impresión y varios</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Cinchos sujetacables</t>
+          <t>Tornillo M2 × 10 + tuerca</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>Paquete corto, negro</t>
+          <t>O autorroscante para plástico</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>Ordenar los cables</t>
+          <t>Finales de carrera (2 por switch)</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
@@ -7254,27 +7219,27 @@
         </is>
       </c>
       <c r="G48" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
-          <t>Recomendado</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>Steren (TY24NE)</t>
+          <t>Vidrí / Casa Rivas</t>
         </is>
       </c>
       <c r="J48" s="26" t="n">
-        <v>2.49</v>
+        <v>0.1</v>
       </c>
       <c r="K48" s="25" t="n">
         <v>1</v>
       </c>
       <c r="L48" s="24" t="inlineStr">
         <is>
-          <t>Verificado en línea 06-oct-2026</t>
+          <t>Estimado</t>
         </is>
       </c>
       <c r="M48" s="26" t="n"/>
@@ -7320,7 +7285,11 @@
       </c>
       <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="23" t="n"/>
-      <c r="AA48" s="30" t="inlineStr"/>
+      <c r="AA48" s="30" t="inlineStr">
+        <is>
+          <t>Si los finales de carrera traen tornillos, no hace falta.</t>
+        </is>
+      </c>
       <c r="AB48" s="28">
         <f>IF(AND(S48="Amazon",ISNUMBER(M48),W48&gt;0),ROUNDUP(G48/N48,0)*M48,0)</f>
         <v/>
@@ -7333,23 +7302,27 @@
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>VAR-03</t>
+          <t>TOR-08</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Impresión y varios</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Funda trenzada para cables 1/4"</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr"/>
+          <t>Perno M5 × 25</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Mazo de cables de la columna</t>
+          <t>Plataforma Z → brazo 1</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
@@ -7358,26 +7331,32 @@
         </is>
       </c>
       <c r="G49" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>Vidrí</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K49" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr"/>
-      <c r="J49" s="26" t="n"/>
-      <c r="K49" s="25" t="n"/>
-      <c r="L49" s="24" t="inlineStr"/>
-      <c r="M49" s="26" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="N49" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="27" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="L49" s="24" t="inlineStr">
+        <is>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="n"/>
+      <c r="N49" s="25" t="n"/>
+      <c r="O49" s="27" t="n"/>
       <c r="P49" s="28">
         <f>IF(J49="","",ROUNDUP(G49/K49,0)*J49*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I49)),DescCasaRivas,0)))</f>
         <v/>
@@ -7392,7 +7371,7 @@
       </c>
       <c r="S49" s="25" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="T49" s="28">
@@ -7401,7 +7380,7 @@
       </c>
       <c r="U49" s="25" t="inlineStr">
         <is>
-          <t>No comprar</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="V49" s="28">
@@ -7417,12 +7396,12 @@
         <v/>
       </c>
       <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="29" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B07RZXSJBM</t>
-        </is>
-      </c>
-      <c r="AA49" s="30" t="inlineStr"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="30" t="inlineStr">
+        <is>
+          <t>Medida del simulador (Z-axis Mount Platform).</t>
+        </is>
+      </c>
       <c r="AB49" s="28">
         <f>IF(AND(S49="Amazon",ISNUMBER(M49),W49&gt;0),ROUNDUP(G49/N49,0)*M49,0)</f>
         <v/>
@@ -7435,7 +7414,7 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>VAR-04</t>
+          <t>VAR-01</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
@@ -7445,52 +7424,57 @@
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Tubo termorretráctil (surtido)</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr"/>
+          <t>Filamento PLA+ 1.75 mm</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>Rollo de 1 kg</t>
+        </is>
+      </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>Aislar empalmes</t>
+          <t>Todas las piezas impresas (ver hoja Impresión 3D)</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>MathBot</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>1</v>
+          <t>HTM</t>
+        </is>
+      </c>
+      <c r="G50" s="31">
+        <f>'Impresión 3D'!$B$6</f>
+        <v/>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
-          <t>Recomendado</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>Casa Rivas</t>
+          <t>El Changarro (PLA 1 kg)</t>
         </is>
       </c>
       <c r="J50" s="26" t="n">
-        <v>2</v>
+        <v>27.99</v>
       </c>
       <c r="K50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="L50" s="24" t="inlineStr">
         <is>
-          <t>Estimado</t>
+          <t>Indexado en buscador (oferta)</t>
         </is>
       </c>
       <c r="M50" s="26" t="n">
-        <v>6.64</v>
+        <v>11.19</v>
       </c>
       <c r="N50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="O50" s="27" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="P50" s="28">
         <f>IF(J50="","",ROUNDUP(G50/K50,0)*J50*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I50)),DescCasaRivas,0)))</f>
@@ -7506,7 +7490,7 @@
       </c>
       <c r="S50" s="25" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="T50" s="28">
@@ -7515,7 +7499,7 @@
       </c>
       <c r="U50" s="25" t="inlineStr">
         <is>
-          <t>Por comprar</t>
+          <t>Ya lo tenemos</t>
         </is>
       </c>
       <c r="V50" s="28">
@@ -7533,10 +7517,14 @@
       <c r="Y50" s="25" t="n"/>
       <c r="Z50" s="29" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B01MFA3OFA</t>
-        </is>
-      </c>
-      <c r="AA50" s="30" t="inlineStr"/>
+          <t>https://www.amazon.com/dp/B07XG3RM58</t>
+        </is>
+      </c>
+      <c r="AA50" s="30" t="inlineStr">
+        <is>
+          <t>Impresión gratuita: todas las piezas impresas quedan sin costo. Avalon Tech publicaba USD 30, pero cerró su tienda en línea en jul-2026: preguntar por WhatsApp. Si la universidad imprime, poner 'Ya lo tenemos'.</t>
+        </is>
+      </c>
       <c r="AB50" s="28">
         <f>IF(AND(S50="Amazon",ISNUMBER(M50),W50&gt;0),ROUNDUP(G50/N50,0)*M50,0)</f>
         <v/>
@@ -7549,7 +7537,7 @@
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>VAR-05</t>
+          <t>VAR-02</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
@@ -7559,44 +7547,46 @@
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Gestión de casillero (por envío)</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr"/>
+          <t>Cinchos sujetacables</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Paquete corto, negro</t>
+        </is>
+      </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Cargo fijo por paquete consolidado</t>
+          <t>Ordenar los cables</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>MathBot</t>
-        </is>
-      </c>
-      <c r="G51" s="31">
-        <f>EnviosCasillero</f>
-        <v/>
+          <t>HTM</t>
+        </is>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Recomendado</t>
         </is>
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>Casillero en Miami (p. ej. QuickBox)</t>
-        </is>
-      </c>
-      <c r="J51" s="32">
-        <f>GestionEnvio</f>
-        <v/>
+          <t>Steren (TY24NE)</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="n">
+        <v>2.49</v>
       </c>
       <c r="K51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="L51" s="24" t="inlineStr">
         <is>
-          <t>Estimado</t>
+          <t>Verificado en línea 06-oct-2026</t>
         </is>
       </c>
       <c r="M51" s="26" t="n"/>
@@ -7642,11 +7632,7 @@
       </c>
       <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="23" t="n"/>
-      <c r="AA51" s="30" t="inlineStr">
-        <is>
-          <t>El flete por libra ya va dentro del 'Total Amazon puesto en SV'. Esta línea es solo la gestión; ajusten el número de envíos en Supuestos.</t>
-        </is>
-      </c>
+      <c r="AA51" s="30" t="inlineStr"/>
       <c r="AB51" s="28">
         <f>IF(AND(S51="Amazon",ISNUMBER(M51),W51&gt;0),ROUNDUP(G51/N51,0)*M51,0)</f>
         <v/>
@@ -7657,140 +7643,466 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>VAR-03</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Impresión y varios</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>Funda trenzada para cables 1/4"</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr"/>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Mazo de cables de la columna</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>HTM</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr"/>
+      <c r="J52" s="26" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="24" t="inlineStr"/>
+      <c r="M52" s="26" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="N52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P52" s="28">
+        <f>IF(J52="","",ROUNDUP(G52/K52,0)*J52*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I52)),DescCasaRivas,0)))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="28">
+        <f>IF(M52="","",ROUNDUP(G52/N52,0)*(M52*(1+TasaVentasEEUU)+O52*FleteLb*(1+IVA)+M52*(1+RecargoCIF)*IVA))</f>
+        <v/>
+      </c>
+      <c r="R52" s="23">
+        <f>IF(AND(ISNUMBER(P52),ISNUMBER(Q52)),IF(P52&lt;=Q52,"Local","Amazon"),IF(ISNUMBER(P52),"Local",IF(ISNUMBER(Q52),"Amazon","—")))</f>
+        <v/>
+      </c>
+      <c r="S52" s="25" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="T52" s="28">
+        <f>IF(S52="Amazon",IF(ISNUMBER(Q52),Q52,0),IF(ISNUMBER(P52),P52,0))</f>
+        <v/>
+      </c>
+      <c r="U52" s="25" t="inlineStr">
+        <is>
+          <t>No comprar</t>
+        </is>
+      </c>
+      <c r="V52" s="28">
+        <f>SUMIFS('Registro de gastos'!$F$10:$F$400,'Registro de gastos'!$B$10:$B$400,A52)</f>
+        <v/>
+      </c>
+      <c r="W52" s="28">
+        <f>IF(OR(U52="Por comprar",U52="Cotizado"),MAX(T52-V52,0),0)</f>
+        <v/>
+      </c>
+      <c r="X52" s="28">
+        <f>V52+W52</f>
+        <v/>
+      </c>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B07RZXSJBM</t>
+        </is>
+      </c>
+      <c r="AA52" s="30" t="inlineStr"/>
+      <c r="AB52" s="28">
+        <f>IF(AND(S52="Amazon",ISNUMBER(M52),W52&gt;0),ROUNDUP(G52/N52,0)*M52,0)</f>
+        <v/>
+      </c>
+      <c r="AC52" s="28">
+        <f>IF(AND(ISNUMBER(P52),ISNUMBER(Q52)),MIN(P52,Q52),IF(ISNUMBER(P52),P52,IF(ISNUMBER(Q52),Q52,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>VAR-04</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Impresión y varios</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>Tubo termorretráctil (surtido)</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr"/>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>Aislar empalmes</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>MathBot</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>Casa Rivas</t>
+        </is>
+      </c>
+      <c r="J53" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="24" t="inlineStr">
+        <is>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="N53" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P53" s="28">
+        <f>IF(J53="","",ROUNDUP(G53/K53,0)*J53*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I53)),DescCasaRivas,0)))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="28">
+        <f>IF(M53="","",ROUNDUP(G53/N53,0)*(M53*(1+TasaVentasEEUU)+O53*FleteLb*(1+IVA)+M53*(1+RecargoCIF)*IVA))</f>
+        <v/>
+      </c>
+      <c r="R53" s="23">
+        <f>IF(AND(ISNUMBER(P53),ISNUMBER(Q53)),IF(P53&lt;=Q53,"Local","Amazon"),IF(ISNUMBER(P53),"Local",IF(ISNUMBER(Q53),"Amazon","—")))</f>
+        <v/>
+      </c>
+      <c r="S53" s="25" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="T53" s="28">
+        <f>IF(S53="Amazon",IF(ISNUMBER(Q53),Q53,0),IF(ISNUMBER(P53),P53,0))</f>
+        <v/>
+      </c>
+      <c r="U53" s="25" t="inlineStr">
+        <is>
+          <t>Por comprar</t>
+        </is>
+      </c>
+      <c r="V53" s="28">
+        <f>SUMIFS('Registro de gastos'!$F$10:$F$400,'Registro de gastos'!$B$10:$B$400,A53)</f>
+        <v/>
+      </c>
+      <c r="W53" s="28">
+        <f>IF(OR(U53="Por comprar",U53="Cotizado"),MAX(T53-V53,0),0)</f>
+        <v/>
+      </c>
+      <c r="X53" s="28">
+        <f>V53+W53</f>
+        <v/>
+      </c>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B01MFA3OFA</t>
+        </is>
+      </c>
+      <c r="AA53" s="30" t="inlineStr"/>
+      <c r="AB53" s="28">
+        <f>IF(AND(S53="Amazon",ISNUMBER(M53),W53&gt;0),ROUNDUP(G53/N53,0)*M53,0)</f>
+        <v/>
+      </c>
+      <c r="AC53" s="28">
+        <f>IF(AND(ISNUMBER(P53),ISNUMBER(Q53)),MIN(P53,Q53),IF(ISNUMBER(P53),P53,IF(ISNUMBER(Q53),Q53,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>VAR-05</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>Impresión y varios</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>Gestión de casillero (por envío)</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>Cargo fijo por paquete consolidado</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>MathBot</t>
+        </is>
+      </c>
+      <c r="G54" s="31">
+        <f>EnviosCasillero</f>
+        <v/>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Casillero en Miami (p. ej. QuickBox)</t>
+        </is>
+      </c>
+      <c r="J54" s="32">
+        <f>GestionEnvio</f>
+        <v/>
+      </c>
+      <c r="K54" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="M54" s="26" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="O54" s="27" t="n"/>
+      <c r="P54" s="28">
+        <f>IF(J54="","",ROUNDUP(G54/K54,0)*J54*(1-IF(ISNUMBER(SEARCH("Casa Rivas",I54)),DescCasaRivas,0)))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="28">
+        <f>IF(M54="","",ROUNDUP(G54/N54,0)*(M54*(1+TasaVentasEEUU)+O54*FleteLb*(1+IVA)+M54*(1+RecargoCIF)*IVA))</f>
+        <v/>
+      </c>
+      <c r="R54" s="23">
+        <f>IF(AND(ISNUMBER(P54),ISNUMBER(Q54)),IF(P54&lt;=Q54,"Local","Amazon"),IF(ISNUMBER(P54),"Local",IF(ISNUMBER(Q54),"Amazon","—")))</f>
+        <v/>
+      </c>
+      <c r="S54" s="25" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="T54" s="28">
+        <f>IF(S54="Amazon",IF(ISNUMBER(Q54),Q54,0),IF(ISNUMBER(P54),P54,0))</f>
+        <v/>
+      </c>
+      <c r="U54" s="25" t="inlineStr">
+        <is>
+          <t>Por comprar</t>
+        </is>
+      </c>
+      <c r="V54" s="28">
+        <f>SUMIFS('Registro de gastos'!$F$10:$F$400,'Registro de gastos'!$B$10:$B$400,A54)</f>
+        <v/>
+      </c>
+      <c r="W54" s="28">
+        <f>IF(OR(U54="Por comprar",U54="Cotizado"),MAX(T54-V54,0),0)</f>
+        <v/>
+      </c>
+      <c r="X54" s="28">
+        <f>V54+W54</f>
+        <v/>
+      </c>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="23" t="n"/>
+      <c r="AA54" s="30" t="inlineStr">
+        <is>
+          <t>El flete por libra ya va dentro del 'Total Amazon puesto en SV'. Esta línea es solo la gestión; ajusten el número de envíos en Supuestos.</t>
+        </is>
+      </c>
+      <c r="AB54" s="28">
+        <f>IF(AND(S54="Amazon",ISNUMBER(M54),W54&gt;0),ROUNDUP(G54/N54,0)*M54,0)</f>
+        <v/>
+      </c>
+      <c r="AC54" s="28">
+        <f>IF(AND(ISNUMBER(P54),ISNUMBER(Q54)),MIN(P54,Q54),IF(ISNUMBER(P54),P54,IF(ISNUMBER(Q54),Q54,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Totales</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="33">
-        <f>SUM(P5:P51)</f>
-        <v/>
-      </c>
-      <c r="Q52" s="33">
-        <f>SUM(Q5:Q51)</f>
-        <v/>
-      </c>
-      <c r="R52" s="2" t="n"/>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="33">
-        <f>SUM(T5:T51)</f>
-        <v/>
-      </c>
-      <c r="U52" s="2" t="n"/>
-      <c r="V52" s="33">
-        <f>SUM(V5:V51)</f>
-        <v/>
-      </c>
-      <c r="W52" s="33">
-        <f>SUM(W5:W51)</f>
-        <v/>
-      </c>
-      <c r="X52" s="33">
-        <f>SUM(X5:X51)</f>
-        <v/>
-      </c>
-      <c r="Y52" s="2" t="n"/>
-      <c r="Z52" s="2" t="n"/>
-      <c r="AA52" s="2" t="n"/>
-      <c r="AB52" s="33">
-        <f>SUM(AB5:AB51)</f>
-        <v/>
-      </c>
-      <c r="AC52" s="33">
-        <f>SUM(AC5:AC51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="33">
+        <f>SUM(P5:P54)</f>
+        <v/>
+      </c>
+      <c r="Q55" s="33">
+        <f>SUM(Q5:Q54)</f>
+        <v/>
+      </c>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="33">
+        <f>SUM(T5:T54)</f>
+        <v/>
+      </c>
+      <c r="U55" s="2" t="n"/>
+      <c r="V55" s="33">
+        <f>SUM(V5:V54)</f>
+        <v/>
+      </c>
+      <c r="W55" s="33">
+        <f>SUM(W5:W54)</f>
+        <v/>
+      </c>
+      <c r="X55" s="33">
+        <f>SUM(X5:X54)</f>
+        <v/>
+      </c>
+      <c r="Y55" s="2" t="n"/>
+      <c r="Z55" s="2" t="n"/>
+      <c r="AA55" s="2" t="n"/>
+      <c r="AB55" s="33">
+        <f>SUM(AB5:AB54)</f>
+        <v/>
+      </c>
+      <c r="AC55" s="33">
+        <f>SUM(AC5:AC54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Nota: 'Total local' y 'Total Amazon' suman todas las filas aunque no se compren; el costo real del proyecto está en 'Proyección'.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="n"/>
-      <c r="S53" s="2" t="n"/>
-      <c r="T53" s="2" t="n"/>
-      <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="n"/>
-      <c r="W53" s="2" t="n"/>
-      <c r="X53" s="2" t="n"/>
-      <c r="Y53" s="2" t="n"/>
-      <c r="Z53" s="2" t="n"/>
-      <c r="AA53" s="2" t="n"/>
-      <c r="AB53" s="2" t="n"/>
-      <c r="AC53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="n"/>
+      <c r="U56" s="2" t="n"/>
+      <c r="V56" s="2" t="n"/>
+      <c r="W56" s="2" t="n"/>
+      <c r="X56" s="2" t="n"/>
+      <c r="Y56" s="2" t="n"/>
+      <c r="Z56" s="2" t="n"/>
+      <c r="AA56" s="2" t="n"/>
+      <c r="AB56" s="2" t="n"/>
+      <c r="AC56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Naranja en 'Fuente elegida' = hay una opción más barata. Gris = fila que no se compra (no suma).</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="n"/>
-      <c r="R54" s="2" t="n"/>
-      <c r="S54" s="2" t="n"/>
-      <c r="T54" s="2" t="n"/>
-      <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="n"/>
-      <c r="W54" s="2" t="n"/>
-      <c r="X54" s="2" t="n"/>
-      <c r="Y54" s="2" t="n"/>
-      <c r="Z54" s="2" t="n"/>
-      <c r="AA54" s="2" t="n"/>
-      <c r="AB54" s="2" t="n"/>
-      <c r="AC54" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="n"/>
+      <c r="U57" s="2" t="n"/>
+      <c r="V57" s="2" t="n"/>
+      <c r="W57" s="2" t="n"/>
+      <c r="X57" s="2" t="n"/>
+      <c r="Y57" s="2" t="n"/>
+      <c r="Z57" s="2" t="n"/>
+      <c r="AA57" s="2" t="n"/>
+      <c r="AB57" s="2" t="n"/>
+      <c r="AC57" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AC51"/>
+  <autoFilter ref="A4:AC54"/>
   <mergeCells count="1">
     <mergeCell ref="A2:AB2"/>
   </mergeCells>
-  <conditionalFormatting sqref="U5:U51">
+  <conditionalFormatting sqref="U5:U54">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Comprado"</formula>
     </cfRule>
@@ -7804,27 +8116,27 @@
       <formula>"No comprar"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S51">
+  <conditionalFormatting sqref="S5:S54">
     <cfRule type="expression" priority="5" dxfId="6">
       <formula>AND(R5&lt;&gt;"—",S5&lt;&gt;R5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:AB51">
+  <conditionalFormatting sqref="A5:AB54">
     <cfRule type="expression" priority="6" dxfId="7">
       <formula>$U5="No comprar"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="U5:U51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="U5:U54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Por comprar,Cotizado,Comprado,Ya lo tenemos,No comprar"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="S5:S54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Local,Amazon"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Obligatorio,Recomendado,Opcional"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y5:Y51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y5:Y54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Miembros</formula1>
     </dataValidation>
   </dataValidations>
@@ -7858,10 +8170,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z35" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z36" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z40" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z47" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z49" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z50" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z42" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z50" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z52" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z53" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8157,7 +8469,7 @@
       <c r="A10" s="37" t="n"/>
       <c r="B10" s="38" t="n"/>
       <c r="C10" s="39">
-        <f>IF(B10="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B10,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B10="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B10,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D10" s="38" t="n"/>
@@ -8177,7 +8489,7 @@
       <c r="A11" s="37" t="n"/>
       <c r="B11" s="38" t="n"/>
       <c r="C11" s="39">
-        <f>IF(B11="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B11,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B11="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B11,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D11" s="38" t="n"/>
@@ -8194,7 +8506,7 @@
       <c r="A12" s="37" t="n"/>
       <c r="B12" s="38" t="n"/>
       <c r="C12" s="39">
-        <f>IF(B12="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B12,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B12="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B12,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D12" s="38" t="n"/>
@@ -8211,7 +8523,7 @@
       <c r="A13" s="37" t="n"/>
       <c r="B13" s="38" t="n"/>
       <c r="C13" s="39">
-        <f>IF(B13="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B13,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B13="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B13,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D13" s="38" t="n"/>
@@ -8228,7 +8540,7 @@
       <c r="A14" s="37" t="n"/>
       <c r="B14" s="38" t="n"/>
       <c r="C14" s="39">
-        <f>IF(B14="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B14,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B14="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B14,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D14" s="38" t="n"/>
@@ -8245,7 +8557,7 @@
       <c r="A15" s="37" t="n"/>
       <c r="B15" s="38" t="n"/>
       <c r="C15" s="39">
-        <f>IF(B15="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B15,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B15="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B15,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D15" s="38" t="n"/>
@@ -8262,7 +8574,7 @@
       <c r="A16" s="37" t="n"/>
       <c r="B16" s="38" t="n"/>
       <c r="C16" s="39">
-        <f>IF(B16="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B16,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B16="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B16,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D16" s="38" t="n"/>
@@ -8279,7 +8591,7 @@
       <c r="A17" s="37" t="n"/>
       <c r="B17" s="38" t="n"/>
       <c r="C17" s="39">
-        <f>IF(B17="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B17,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B17="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B17,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D17" s="38" t="n"/>
@@ -8296,7 +8608,7 @@
       <c r="A18" s="37" t="n"/>
       <c r="B18" s="38" t="n"/>
       <c r="C18" s="39">
-        <f>IF(B18="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B18,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B18="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B18,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D18" s="38" t="n"/>
@@ -8313,7 +8625,7 @@
       <c r="A19" s="37" t="n"/>
       <c r="B19" s="38" t="n"/>
       <c r="C19" s="39">
-        <f>IF(B19="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B19,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B19="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B19,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D19" s="38" t="n"/>
@@ -8330,7 +8642,7 @@
       <c r="A20" s="37" t="n"/>
       <c r="B20" s="38" t="n"/>
       <c r="C20" s="39">
-        <f>IF(B20="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B20,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B20="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B20,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D20" s="38" t="n"/>
@@ -8347,7 +8659,7 @@
       <c r="A21" s="37" t="n"/>
       <c r="B21" s="38" t="n"/>
       <c r="C21" s="39">
-        <f>IF(B21="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B21,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B21="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B21,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D21" s="38" t="n"/>
@@ -8364,7 +8676,7 @@
       <c r="A22" s="37" t="n"/>
       <c r="B22" s="38" t="n"/>
       <c r="C22" s="39">
-        <f>IF(B22="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B22,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B22="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B22,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D22" s="38" t="n"/>
@@ -8381,7 +8693,7 @@
       <c r="A23" s="37" t="n"/>
       <c r="B23" s="38" t="n"/>
       <c r="C23" s="39">
-        <f>IF(B23="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B23,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B23="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B23,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D23" s="38" t="n"/>
@@ -8398,7 +8710,7 @@
       <c r="A24" s="37" t="n"/>
       <c r="B24" s="38" t="n"/>
       <c r="C24" s="39">
-        <f>IF(B24="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B24,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B24="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B24,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D24" s="38" t="n"/>
@@ -8415,7 +8727,7 @@
       <c r="A25" s="37" t="n"/>
       <c r="B25" s="38" t="n"/>
       <c r="C25" s="39">
-        <f>IF(B25="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B25,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B25="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B25,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D25" s="38" t="n"/>
@@ -8432,7 +8744,7 @@
       <c r="A26" s="37" t="n"/>
       <c r="B26" s="38" t="n"/>
       <c r="C26" s="39">
-        <f>IF(B26="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B26,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B26="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B26,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D26" s="38" t="n"/>
@@ -8449,7 +8761,7 @@
       <c r="A27" s="37" t="n"/>
       <c r="B27" s="38" t="n"/>
       <c r="C27" s="39">
-        <f>IF(B27="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B27,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B27="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B27,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D27" s="38" t="n"/>
@@ -8466,7 +8778,7 @@
       <c r="A28" s="37" t="n"/>
       <c r="B28" s="38" t="n"/>
       <c r="C28" s="39">
-        <f>IF(B28="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B28,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B28="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B28,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D28" s="38" t="n"/>
@@ -8483,7 +8795,7 @@
       <c r="A29" s="37" t="n"/>
       <c r="B29" s="38" t="n"/>
       <c r="C29" s="39">
-        <f>IF(B29="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B29,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B29="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B29,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D29" s="38" t="n"/>
@@ -8500,7 +8812,7 @@
       <c r="A30" s="37" t="n"/>
       <c r="B30" s="38" t="n"/>
       <c r="C30" s="39">
-        <f>IF(B30="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B30,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B30="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B30,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D30" s="38" t="n"/>
@@ -8517,7 +8829,7 @@
       <c r="A31" s="37" t="n"/>
       <c r="B31" s="38" t="n"/>
       <c r="C31" s="39">
-        <f>IF(B31="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B31,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B31="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B31,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D31" s="38" t="n"/>
@@ -8534,7 +8846,7 @@
       <c r="A32" s="37" t="n"/>
       <c r="B32" s="38" t="n"/>
       <c r="C32" s="39">
-        <f>IF(B32="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B32,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B32="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B32,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D32" s="38" t="n"/>
@@ -8551,7 +8863,7 @@
       <c r="A33" s="37" t="n"/>
       <c r="B33" s="38" t="n"/>
       <c r="C33" s="39">
-        <f>IF(B33="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B33,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B33="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B33,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D33" s="38" t="n"/>
@@ -8568,7 +8880,7 @@
       <c r="A34" s="37" t="n"/>
       <c r="B34" s="38" t="n"/>
       <c r="C34" s="39">
-        <f>IF(B34="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B34,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B34="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B34,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D34" s="38" t="n"/>
@@ -8585,7 +8897,7 @@
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="38" t="n"/>
       <c r="C35" s="39">
-        <f>IF(B35="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B35,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B35="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B35,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D35" s="38" t="n"/>
@@ -8602,7 +8914,7 @@
       <c r="A36" s="37" t="n"/>
       <c r="B36" s="38" t="n"/>
       <c r="C36" s="39">
-        <f>IF(B36="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B36,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B36="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B36,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D36" s="38" t="n"/>
@@ -8619,7 +8931,7 @@
       <c r="A37" s="37" t="n"/>
       <c r="B37" s="38" t="n"/>
       <c r="C37" s="39">
-        <f>IF(B37="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B37,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B37="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B37,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D37" s="38" t="n"/>
@@ -8636,7 +8948,7 @@
       <c r="A38" s="37" t="n"/>
       <c r="B38" s="38" t="n"/>
       <c r="C38" s="39">
-        <f>IF(B38="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B38,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B38="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B38,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D38" s="38" t="n"/>
@@ -8653,7 +8965,7 @@
       <c r="A39" s="37" t="n"/>
       <c r="B39" s="38" t="n"/>
       <c r="C39" s="39">
-        <f>IF(B39="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B39,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B39="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B39,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D39" s="38" t="n"/>
@@ -8670,7 +8982,7 @@
       <c r="A40" s="37" t="n"/>
       <c r="B40" s="38" t="n"/>
       <c r="C40" s="39">
-        <f>IF(B40="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B40,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B40="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B40,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D40" s="38" t="n"/>
@@ -8687,7 +8999,7 @@
       <c r="A41" s="37" t="n"/>
       <c r="B41" s="38" t="n"/>
       <c r="C41" s="39">
-        <f>IF(B41="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B41,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B41="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B41,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D41" s="38" t="n"/>
@@ -8704,7 +9016,7 @@
       <c r="A42" s="37" t="n"/>
       <c r="B42" s="38" t="n"/>
       <c r="C42" s="39">
-        <f>IF(B42="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B42,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B42="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B42,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D42" s="38" t="n"/>
@@ -8721,7 +9033,7 @@
       <c r="A43" s="37" t="n"/>
       <c r="B43" s="38" t="n"/>
       <c r="C43" s="39">
-        <f>IF(B43="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B43,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B43="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B43,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D43" s="38" t="n"/>
@@ -8738,7 +9050,7 @@
       <c r="A44" s="37" t="n"/>
       <c r="B44" s="38" t="n"/>
       <c r="C44" s="39">
-        <f>IF(B44="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B44,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B44="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B44,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D44" s="38" t="n"/>
@@ -8755,7 +9067,7 @@
       <c r="A45" s="37" t="n"/>
       <c r="B45" s="38" t="n"/>
       <c r="C45" s="39">
-        <f>IF(B45="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B45,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B45="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B45,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D45" s="38" t="n"/>
@@ -8772,7 +9084,7 @@
       <c r="A46" s="37" t="n"/>
       <c r="B46" s="38" t="n"/>
       <c r="C46" s="39">
-        <f>IF(B46="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B46,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B46="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B46,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D46" s="38" t="n"/>
@@ -8789,7 +9101,7 @@
       <c r="A47" s="37" t="n"/>
       <c r="B47" s="38" t="n"/>
       <c r="C47" s="39">
-        <f>IF(B47="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B47,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B47="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B47,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D47" s="38" t="n"/>
@@ -8806,7 +9118,7 @@
       <c r="A48" s="37" t="n"/>
       <c r="B48" s="38" t="n"/>
       <c r="C48" s="39">
-        <f>IF(B48="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B48,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B48="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B48,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D48" s="38" t="n"/>
@@ -8823,7 +9135,7 @@
       <c r="A49" s="37" t="n"/>
       <c r="B49" s="38" t="n"/>
       <c r="C49" s="39">
-        <f>IF(B49="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B49,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B49="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B49,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D49" s="38" t="n"/>
@@ -8840,7 +9152,7 @@
       <c r="A50" s="37" t="n"/>
       <c r="B50" s="38" t="n"/>
       <c r="C50" s="39">
-        <f>IF(B50="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B50,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B50="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B50,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D50" s="38" t="n"/>
@@ -8857,7 +9169,7 @@
       <c r="A51" s="37" t="n"/>
       <c r="B51" s="38" t="n"/>
       <c r="C51" s="39">
-        <f>IF(B51="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B51,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B51="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B51,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D51" s="38" t="n"/>
@@ -8874,7 +9186,7 @@
       <c r="A52" s="37" t="n"/>
       <c r="B52" s="38" t="n"/>
       <c r="C52" s="39">
-        <f>IF(B52="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B52,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B52="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B52,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D52" s="38" t="n"/>
@@ -8891,7 +9203,7 @@
       <c r="A53" s="37" t="n"/>
       <c r="B53" s="38" t="n"/>
       <c r="C53" s="39">
-        <f>IF(B53="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B53,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B53="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B53,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D53" s="38" t="n"/>
@@ -8908,7 +9220,7 @@
       <c r="A54" s="37" t="n"/>
       <c r="B54" s="38" t="n"/>
       <c r="C54" s="39">
-        <f>IF(B54="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B54,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B54="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B54,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D54" s="38" t="n"/>
@@ -8925,7 +9237,7 @@
       <c r="A55" s="37" t="n"/>
       <c r="B55" s="38" t="n"/>
       <c r="C55" s="39">
-        <f>IF(B55="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B55,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B55="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B55,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D55" s="38" t="n"/>
@@ -8942,7 +9254,7 @@
       <c r="A56" s="37" t="n"/>
       <c r="B56" s="38" t="n"/>
       <c r="C56" s="39">
-        <f>IF(B56="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B56,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B56="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B56,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D56" s="38" t="n"/>
@@ -8959,7 +9271,7 @@
       <c r="A57" s="37" t="n"/>
       <c r="B57" s="38" t="n"/>
       <c r="C57" s="39">
-        <f>IF(B57="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B57,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B57="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B57,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D57" s="38" t="n"/>
@@ -8976,7 +9288,7 @@
       <c r="A58" s="37" t="n"/>
       <c r="B58" s="38" t="n"/>
       <c r="C58" s="39">
-        <f>IF(B58="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B58,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B58="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B58,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D58" s="38" t="n"/>
@@ -8993,7 +9305,7 @@
       <c r="A59" s="37" t="n"/>
       <c r="B59" s="38" t="n"/>
       <c r="C59" s="39">
-        <f>IF(B59="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B59,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B59="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B59,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D59" s="38" t="n"/>
@@ -9010,7 +9322,7 @@
       <c r="A60" s="42" t="n"/>
       <c r="B60" s="43" t="n"/>
       <c r="C60" s="5">
-        <f>IF(B60="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B60,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B60="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B60,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D60" s="43" t="n"/>
@@ -9027,7 +9339,7 @@
       <c r="A61" s="42" t="n"/>
       <c r="B61" s="43" t="n"/>
       <c r="C61" s="5">
-        <f>IF(B61="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B61,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B61="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B61,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D61" s="43" t="n"/>
@@ -9044,7 +9356,7 @@
       <c r="A62" s="42" t="n"/>
       <c r="B62" s="43" t="n"/>
       <c r="C62" s="5">
-        <f>IF(B62="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B62,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B62="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B62,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D62" s="43" t="n"/>
@@ -9061,7 +9373,7 @@
       <c r="A63" s="42" t="n"/>
       <c r="B63" s="43" t="n"/>
       <c r="C63" s="5">
-        <f>IF(B63="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B63,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B63="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B63,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D63" s="43" t="n"/>
@@ -9078,7 +9390,7 @@
       <c r="A64" s="42" t="n"/>
       <c r="B64" s="43" t="n"/>
       <c r="C64" s="5">
-        <f>IF(B64="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B64,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B64="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B64,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D64" s="43" t="n"/>
@@ -9095,7 +9407,7 @@
       <c r="A65" s="42" t="n"/>
       <c r="B65" s="43" t="n"/>
       <c r="C65" s="5">
-        <f>IF(B65="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B65,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B65="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B65,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D65" s="43" t="n"/>
@@ -9112,7 +9424,7 @@
       <c r="A66" s="42" t="n"/>
       <c r="B66" s="43" t="n"/>
       <c r="C66" s="5">
-        <f>IF(B66="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B66,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B66="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B66,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D66" s="43" t="n"/>
@@ -9129,7 +9441,7 @@
       <c r="A67" s="42" t="n"/>
       <c r="B67" s="43" t="n"/>
       <c r="C67" s="5">
-        <f>IF(B67="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B67,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B67="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B67,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D67" s="43" t="n"/>
@@ -9146,7 +9458,7 @@
       <c r="A68" s="42" t="n"/>
       <c r="B68" s="43" t="n"/>
       <c r="C68" s="5">
-        <f>IF(B68="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B68,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B68="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B68,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D68" s="43" t="n"/>
@@ -9163,7 +9475,7 @@
       <c r="A69" s="42" t="n"/>
       <c r="B69" s="43" t="n"/>
       <c r="C69" s="5">
-        <f>IF(B69="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B69,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B69="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B69,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D69" s="43" t="n"/>
@@ -9180,7 +9492,7 @@
       <c r="A70" s="42" t="n"/>
       <c r="B70" s="43" t="n"/>
       <c r="C70" s="5">
-        <f>IF(B70="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B70,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B70="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B70,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D70" s="43" t="n"/>
@@ -9197,7 +9509,7 @@
       <c r="A71" s="42" t="n"/>
       <c r="B71" s="43" t="n"/>
       <c r="C71" s="5">
-        <f>IF(B71="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B71,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B71="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B71,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D71" s="43" t="n"/>
@@ -9214,7 +9526,7 @@
       <c r="A72" s="42" t="n"/>
       <c r="B72" s="43" t="n"/>
       <c r="C72" s="5">
-        <f>IF(B72="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B72,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B72="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B72,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D72" s="43" t="n"/>
@@ -9231,7 +9543,7 @@
       <c r="A73" s="42" t="n"/>
       <c r="B73" s="43" t="n"/>
       <c r="C73" s="5">
-        <f>IF(B73="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B73,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B73="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B73,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D73" s="43" t="n"/>
@@ -9248,7 +9560,7 @@
       <c r="A74" s="42" t="n"/>
       <c r="B74" s="43" t="n"/>
       <c r="C74" s="5">
-        <f>IF(B74="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B74,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B74="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B74,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D74" s="43" t="n"/>
@@ -9265,7 +9577,7 @@
       <c r="A75" s="42" t="n"/>
       <c r="B75" s="43" t="n"/>
       <c r="C75" s="5">
-        <f>IF(B75="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B75,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B75="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B75,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D75" s="43" t="n"/>
@@ -9282,7 +9594,7 @@
       <c r="A76" s="42" t="n"/>
       <c r="B76" s="43" t="n"/>
       <c r="C76" s="5">
-        <f>IF(B76="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B76,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B76="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B76,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D76" s="43" t="n"/>
@@ -9299,7 +9611,7 @@
       <c r="A77" s="42" t="n"/>
       <c r="B77" s="43" t="n"/>
       <c r="C77" s="5">
-        <f>IF(B77="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B77,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B77="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B77,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D77" s="43" t="n"/>
@@ -9316,7 +9628,7 @@
       <c r="A78" s="42" t="n"/>
       <c r="B78" s="43" t="n"/>
       <c r="C78" s="5">
-        <f>IF(B78="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B78,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B78="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B78,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D78" s="43" t="n"/>
@@ -9333,7 +9645,7 @@
       <c r="A79" s="42" t="n"/>
       <c r="B79" s="43" t="n"/>
       <c r="C79" s="5">
-        <f>IF(B79="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B79,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B79="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B79,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D79" s="43" t="n"/>
@@ -9350,7 +9662,7 @@
       <c r="A80" s="42" t="n"/>
       <c r="B80" s="43" t="n"/>
       <c r="C80" s="5">
-        <f>IF(B80="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B80,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B80="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B80,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D80" s="43" t="n"/>
@@ -9367,7 +9679,7 @@
       <c r="A81" s="42" t="n"/>
       <c r="B81" s="43" t="n"/>
       <c r="C81" s="5">
-        <f>IF(B81="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B81,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B81="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B81,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D81" s="43" t="n"/>
@@ -9384,7 +9696,7 @@
       <c r="A82" s="42" t="n"/>
       <c r="B82" s="43" t="n"/>
       <c r="C82" s="5">
-        <f>IF(B82="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B82,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B82="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B82,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D82" s="43" t="n"/>
@@ -9401,7 +9713,7 @@
       <c r="A83" s="42" t="n"/>
       <c r="B83" s="43" t="n"/>
       <c r="C83" s="5">
-        <f>IF(B83="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B83,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B83="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B83,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D83" s="43" t="n"/>
@@ -9418,7 +9730,7 @@
       <c r="A84" s="42" t="n"/>
       <c r="B84" s="43" t="n"/>
       <c r="C84" s="5">
-        <f>IF(B84="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B84,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B84="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B84,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D84" s="43" t="n"/>
@@ -9435,7 +9747,7 @@
       <c r="A85" s="42" t="n"/>
       <c r="B85" s="43" t="n"/>
       <c r="C85" s="5">
-        <f>IF(B85="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B85,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B85="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B85,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D85" s="43" t="n"/>
@@ -9452,7 +9764,7 @@
       <c r="A86" s="42" t="n"/>
       <c r="B86" s="43" t="n"/>
       <c r="C86" s="5">
-        <f>IF(B86="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B86,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B86="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B86,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D86" s="43" t="n"/>
@@ -9469,7 +9781,7 @@
       <c r="A87" s="42" t="n"/>
       <c r="B87" s="43" t="n"/>
       <c r="C87" s="5">
-        <f>IF(B87="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B87,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B87="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B87,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D87" s="43" t="n"/>
@@ -9486,7 +9798,7 @@
       <c r="A88" s="42" t="n"/>
       <c r="B88" s="43" t="n"/>
       <c r="C88" s="5">
-        <f>IF(B88="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B88,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B88="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B88,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D88" s="43" t="n"/>
@@ -9503,7 +9815,7 @@
       <c r="A89" s="42" t="n"/>
       <c r="B89" s="43" t="n"/>
       <c r="C89" s="5">
-        <f>IF(B89="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B89,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B89="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B89,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D89" s="43" t="n"/>
@@ -9520,7 +9832,7 @@
       <c r="A90" s="42" t="n"/>
       <c r="B90" s="43" t="n"/>
       <c r="C90" s="5">
-        <f>IF(B90="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B90,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B90="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B90,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D90" s="43" t="n"/>
@@ -9537,7 +9849,7 @@
       <c r="A91" s="42" t="n"/>
       <c r="B91" s="43" t="n"/>
       <c r="C91" s="5">
-        <f>IF(B91="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B91,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B91="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B91,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D91" s="43" t="n"/>
@@ -9554,7 +9866,7 @@
       <c r="A92" s="42" t="n"/>
       <c r="B92" s="43" t="n"/>
       <c r="C92" s="5">
-        <f>IF(B92="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B92,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B92="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B92,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D92" s="43" t="n"/>
@@ -9571,7 +9883,7 @@
       <c r="A93" s="42" t="n"/>
       <c r="B93" s="43" t="n"/>
       <c r="C93" s="5">
-        <f>IF(B93="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B93,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B93="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B93,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D93" s="43" t="n"/>
@@ -9588,7 +9900,7 @@
       <c r="A94" s="42" t="n"/>
       <c r="B94" s="43" t="n"/>
       <c r="C94" s="5">
-        <f>IF(B94="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B94,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B94="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B94,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D94" s="43" t="n"/>
@@ -9605,7 +9917,7 @@
       <c r="A95" s="42" t="n"/>
       <c r="B95" s="43" t="n"/>
       <c r="C95" s="5">
-        <f>IF(B95="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B95,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B95="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B95,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D95" s="43" t="n"/>
@@ -9622,7 +9934,7 @@
       <c r="A96" s="42" t="n"/>
       <c r="B96" s="43" t="n"/>
       <c r="C96" s="5">
-        <f>IF(B96="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B96,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B96="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B96,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D96" s="43" t="n"/>
@@ -9639,7 +9951,7 @@
       <c r="A97" s="42" t="n"/>
       <c r="B97" s="43" t="n"/>
       <c r="C97" s="5">
-        <f>IF(B97="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B97,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B97="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B97,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D97" s="43" t="n"/>
@@ -9656,7 +9968,7 @@
       <c r="A98" s="42" t="n"/>
       <c r="B98" s="43" t="n"/>
       <c r="C98" s="5">
-        <f>IF(B98="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B98,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B98="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B98,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D98" s="43" t="n"/>
@@ -9673,7 +9985,7 @@
       <c r="A99" s="42" t="n"/>
       <c r="B99" s="43" t="n"/>
       <c r="C99" s="5">
-        <f>IF(B99="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B99,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B99="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B99,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D99" s="43" t="n"/>
@@ -9690,7 +10002,7 @@
       <c r="A100" s="42" t="n"/>
       <c r="B100" s="43" t="n"/>
       <c r="C100" s="5">
-        <f>IF(B100="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B100,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B100="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B100,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D100" s="43" t="n"/>
@@ -9707,7 +10019,7 @@
       <c r="A101" s="42" t="n"/>
       <c r="B101" s="43" t="n"/>
       <c r="C101" s="5">
-        <f>IF(B101="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B101,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B101="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B101,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D101" s="43" t="n"/>
@@ -9724,7 +10036,7 @@
       <c r="A102" s="42" t="n"/>
       <c r="B102" s="43" t="n"/>
       <c r="C102" s="5">
-        <f>IF(B102="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B102,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B102="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B102,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D102" s="43" t="n"/>
@@ -9741,7 +10053,7 @@
       <c r="A103" s="42" t="n"/>
       <c r="B103" s="43" t="n"/>
       <c r="C103" s="5">
-        <f>IF(B103="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B103,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B103="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B103,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D103" s="43" t="n"/>
@@ -9758,7 +10070,7 @@
       <c r="A104" s="42" t="n"/>
       <c r="B104" s="43" t="n"/>
       <c r="C104" s="5">
-        <f>IF(B104="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B104,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B104="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B104,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D104" s="43" t="n"/>
@@ -9775,7 +10087,7 @@
       <c r="A105" s="42" t="n"/>
       <c r="B105" s="43" t="n"/>
       <c r="C105" s="5">
-        <f>IF(B105="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B105,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B105="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B105,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D105" s="43" t="n"/>
@@ -9792,7 +10104,7 @@
       <c r="A106" s="42" t="n"/>
       <c r="B106" s="43" t="n"/>
       <c r="C106" s="5">
-        <f>IF(B106="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B106,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B106="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B106,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D106" s="43" t="n"/>
@@ -9809,7 +10121,7 @@
       <c r="A107" s="42" t="n"/>
       <c r="B107" s="43" t="n"/>
       <c r="C107" s="5">
-        <f>IF(B107="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B107,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B107="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B107,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D107" s="43" t="n"/>
@@ -9826,7 +10138,7 @@
       <c r="A108" s="42" t="n"/>
       <c r="B108" s="43" t="n"/>
       <c r="C108" s="5">
-        <f>IF(B108="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B108,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B108="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B108,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D108" s="43" t="n"/>
@@ -9843,7 +10155,7 @@
       <c r="A109" s="42" t="n"/>
       <c r="B109" s="43" t="n"/>
       <c r="C109" s="5">
-        <f>IF(B109="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B109,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B109="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B109,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D109" s="43" t="n"/>
@@ -9860,7 +10172,7 @@
       <c r="A110" s="42" t="n"/>
       <c r="B110" s="43" t="n"/>
       <c r="C110" s="5">
-        <f>IF(B110="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B110,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B110="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B110,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D110" s="43" t="n"/>
@@ -9877,7 +10189,7 @@
       <c r="A111" s="42" t="n"/>
       <c r="B111" s="43" t="n"/>
       <c r="C111" s="5">
-        <f>IF(B111="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B111,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B111="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B111,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D111" s="43" t="n"/>
@@ -9894,7 +10206,7 @@
       <c r="A112" s="42" t="n"/>
       <c r="B112" s="43" t="n"/>
       <c r="C112" s="5">
-        <f>IF(B112="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B112,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B112="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B112,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D112" s="43" t="n"/>
@@ -9911,7 +10223,7 @@
       <c r="A113" s="42" t="n"/>
       <c r="B113" s="43" t="n"/>
       <c r="C113" s="5">
-        <f>IF(B113="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B113,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B113="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B113,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D113" s="43" t="n"/>
@@ -9928,7 +10240,7 @@
       <c r="A114" s="42" t="n"/>
       <c r="B114" s="43" t="n"/>
       <c r="C114" s="5">
-        <f>IF(B114="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B114,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B114="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B114,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D114" s="43" t="n"/>
@@ -9945,7 +10257,7 @@
       <c r="A115" s="42" t="n"/>
       <c r="B115" s="43" t="n"/>
       <c r="C115" s="5">
-        <f>IF(B115="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B115,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B115="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B115,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D115" s="43" t="n"/>
@@ -9962,7 +10274,7 @@
       <c r="A116" s="42" t="n"/>
       <c r="B116" s="43" t="n"/>
       <c r="C116" s="5">
-        <f>IF(B116="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B116,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B116="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B116,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D116" s="43" t="n"/>
@@ -9979,7 +10291,7 @@
       <c r="A117" s="42" t="n"/>
       <c r="B117" s="43" t="n"/>
       <c r="C117" s="5">
-        <f>IF(B117="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B117,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B117="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B117,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D117" s="43" t="n"/>
@@ -9996,7 +10308,7 @@
       <c r="A118" s="42" t="n"/>
       <c r="B118" s="43" t="n"/>
       <c r="C118" s="5">
-        <f>IF(B118="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B118,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B118="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B118,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D118" s="43" t="n"/>
@@ -10013,7 +10325,7 @@
       <c r="A119" s="42" t="n"/>
       <c r="B119" s="43" t="n"/>
       <c r="C119" s="5">
-        <f>IF(B119="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B119,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B119="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B119,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D119" s="43" t="n"/>
@@ -10030,7 +10342,7 @@
       <c r="A120" s="42" t="n"/>
       <c r="B120" s="43" t="n"/>
       <c r="C120" s="5">
-        <f>IF(B120="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B120,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B120="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B120,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D120" s="43" t="n"/>
@@ -10047,7 +10359,7 @@
       <c r="A121" s="42" t="n"/>
       <c r="B121" s="43" t="n"/>
       <c r="C121" s="5">
-        <f>IF(B121="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B121,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B121="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B121,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D121" s="43" t="n"/>
@@ -10064,7 +10376,7 @@
       <c r="A122" s="42" t="n"/>
       <c r="B122" s="43" t="n"/>
       <c r="C122" s="5">
-        <f>IF(B122="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B122,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B122="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B122,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D122" s="43" t="n"/>
@@ -10081,7 +10393,7 @@
       <c r="A123" s="42" t="n"/>
       <c r="B123" s="43" t="n"/>
       <c r="C123" s="5">
-        <f>IF(B123="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B123,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B123="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B123,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D123" s="43" t="n"/>
@@ -10098,7 +10410,7 @@
       <c r="A124" s="42" t="n"/>
       <c r="B124" s="43" t="n"/>
       <c r="C124" s="5">
-        <f>IF(B124="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B124,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B124="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B124,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D124" s="43" t="n"/>
@@ -10115,7 +10427,7 @@
       <c r="A125" s="42" t="n"/>
       <c r="B125" s="43" t="n"/>
       <c r="C125" s="5">
-        <f>IF(B125="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B125,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B125="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B125,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D125" s="43" t="n"/>
@@ -10132,7 +10444,7 @@
       <c r="A126" s="42" t="n"/>
       <c r="B126" s="43" t="n"/>
       <c r="C126" s="5">
-        <f>IF(B126="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B126,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B126="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B126,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D126" s="43" t="n"/>
@@ -10149,7 +10461,7 @@
       <c r="A127" s="42" t="n"/>
       <c r="B127" s="43" t="n"/>
       <c r="C127" s="5">
-        <f>IF(B127="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B127,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B127="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B127,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D127" s="43" t="n"/>
@@ -10166,7 +10478,7 @@
       <c r="A128" s="42" t="n"/>
       <c r="B128" s="43" t="n"/>
       <c r="C128" s="5">
-        <f>IF(B128="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B128,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B128="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B128,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D128" s="43" t="n"/>
@@ -10183,7 +10495,7 @@
       <c r="A129" s="42" t="n"/>
       <c r="B129" s="43" t="n"/>
       <c r="C129" s="5">
-        <f>IF(B129="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B129,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B129="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B129,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D129" s="43" t="n"/>
@@ -10200,7 +10512,7 @@
       <c r="A130" s="42" t="n"/>
       <c r="B130" s="43" t="n"/>
       <c r="C130" s="5">
-        <f>IF(B130="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B130,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B130="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B130,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D130" s="43" t="n"/>
@@ -10217,7 +10529,7 @@
       <c r="A131" s="42" t="n"/>
       <c r="B131" s="43" t="n"/>
       <c r="C131" s="5">
-        <f>IF(B131="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B131,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B131="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B131,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D131" s="43" t="n"/>
@@ -10234,7 +10546,7 @@
       <c r="A132" s="42" t="n"/>
       <c r="B132" s="43" t="n"/>
       <c r="C132" s="5">
-        <f>IF(B132="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B132,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B132="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B132,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D132" s="43" t="n"/>
@@ -10251,7 +10563,7 @@
       <c r="A133" s="42" t="n"/>
       <c r="B133" s="43" t="n"/>
       <c r="C133" s="5">
-        <f>IF(B133="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B133,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B133="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B133,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D133" s="43" t="n"/>
@@ -10268,7 +10580,7 @@
       <c r="A134" s="42" t="n"/>
       <c r="B134" s="43" t="n"/>
       <c r="C134" s="5">
-        <f>IF(B134="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B134,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B134="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B134,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D134" s="43" t="n"/>
@@ -10285,7 +10597,7 @@
       <c r="A135" s="42" t="n"/>
       <c r="B135" s="43" t="n"/>
       <c r="C135" s="5">
-        <f>IF(B135="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B135,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B135="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B135,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D135" s="43" t="n"/>
@@ -10302,7 +10614,7 @@
       <c r="A136" s="42" t="n"/>
       <c r="B136" s="43" t="n"/>
       <c r="C136" s="5">
-        <f>IF(B136="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B136,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B136="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B136,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D136" s="43" t="n"/>
@@ -10319,7 +10631,7 @@
       <c r="A137" s="42" t="n"/>
       <c r="B137" s="43" t="n"/>
       <c r="C137" s="5">
-        <f>IF(B137="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B137,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B137="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B137,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D137" s="43" t="n"/>
@@ -10336,7 +10648,7 @@
       <c r="A138" s="42" t="n"/>
       <c r="B138" s="43" t="n"/>
       <c r="C138" s="5">
-        <f>IF(B138="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B138,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B138="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B138,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D138" s="43" t="n"/>
@@ -10353,7 +10665,7 @@
       <c r="A139" s="42" t="n"/>
       <c r="B139" s="43" t="n"/>
       <c r="C139" s="5">
-        <f>IF(B139="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B139,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B139="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B139,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D139" s="43" t="n"/>
@@ -10370,7 +10682,7 @@
       <c r="A140" s="42" t="n"/>
       <c r="B140" s="43" t="n"/>
       <c r="C140" s="5">
-        <f>IF(B140="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B140,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B140="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B140,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D140" s="43" t="n"/>
@@ -10387,7 +10699,7 @@
       <c r="A141" s="42" t="n"/>
       <c r="B141" s="43" t="n"/>
       <c r="C141" s="5">
-        <f>IF(B141="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B141,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B141="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B141,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D141" s="43" t="n"/>
@@ -10404,7 +10716,7 @@
       <c r="A142" s="42" t="n"/>
       <c r="B142" s="43" t="n"/>
       <c r="C142" s="5">
-        <f>IF(B142="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B142,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B142="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B142,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D142" s="43" t="n"/>
@@ -10421,7 +10733,7 @@
       <c r="A143" s="42" t="n"/>
       <c r="B143" s="43" t="n"/>
       <c r="C143" s="5">
-        <f>IF(B143="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B143,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B143="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B143,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D143" s="43" t="n"/>
@@ -10438,7 +10750,7 @@
       <c r="A144" s="42" t="n"/>
       <c r="B144" s="43" t="n"/>
       <c r="C144" s="5">
-        <f>IF(B144="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B144,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B144="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B144,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D144" s="43" t="n"/>
@@ -10455,7 +10767,7 @@
       <c r="A145" s="42" t="n"/>
       <c r="B145" s="43" t="n"/>
       <c r="C145" s="5">
-        <f>IF(B145="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B145,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B145="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B145,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D145" s="43" t="n"/>
@@ -10472,7 +10784,7 @@
       <c r="A146" s="42" t="n"/>
       <c r="B146" s="43" t="n"/>
       <c r="C146" s="5">
-        <f>IF(B146="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B146,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B146="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B146,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D146" s="43" t="n"/>
@@ -10489,7 +10801,7 @@
       <c r="A147" s="42" t="n"/>
       <c r="B147" s="43" t="n"/>
       <c r="C147" s="5">
-        <f>IF(B147="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B147,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B147="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B147,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D147" s="43" t="n"/>
@@ -10506,7 +10818,7 @@
       <c r="A148" s="42" t="n"/>
       <c r="B148" s="43" t="n"/>
       <c r="C148" s="5">
-        <f>IF(B148="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B148,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B148="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B148,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D148" s="43" t="n"/>
@@ -10523,7 +10835,7 @@
       <c r="A149" s="42" t="n"/>
       <c r="B149" s="43" t="n"/>
       <c r="C149" s="5">
-        <f>IF(B149="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B149,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B149="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B149,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D149" s="43" t="n"/>
@@ -10540,7 +10852,7 @@
       <c r="A150" s="42" t="n"/>
       <c r="B150" s="43" t="n"/>
       <c r="C150" s="5">
-        <f>IF(B150="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B150,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B150="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B150,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D150" s="43" t="n"/>
@@ -10557,7 +10869,7 @@
       <c r="A151" s="42" t="n"/>
       <c r="B151" s="43" t="n"/>
       <c r="C151" s="5">
-        <f>IF(B151="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B151,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B151="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B151,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D151" s="43" t="n"/>
@@ -10574,7 +10886,7 @@
       <c r="A152" s="42" t="n"/>
       <c r="B152" s="43" t="n"/>
       <c r="C152" s="5">
-        <f>IF(B152="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B152,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B152="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B152,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D152" s="43" t="n"/>
@@ -10591,7 +10903,7 @@
       <c r="A153" s="42" t="n"/>
       <c r="B153" s="43" t="n"/>
       <c r="C153" s="5">
-        <f>IF(B153="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B153,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B153="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B153,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D153" s="43" t="n"/>
@@ -10608,7 +10920,7 @@
       <c r="A154" s="42" t="n"/>
       <c r="B154" s="43" t="n"/>
       <c r="C154" s="5">
-        <f>IF(B154="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B154,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B154="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B154,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D154" s="43" t="n"/>
@@ -10625,7 +10937,7 @@
       <c r="A155" s="42" t="n"/>
       <c r="B155" s="43" t="n"/>
       <c r="C155" s="5">
-        <f>IF(B155="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B155,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B155="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B155,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D155" s="43" t="n"/>
@@ -10642,7 +10954,7 @@
       <c r="A156" s="42" t="n"/>
       <c r="B156" s="43" t="n"/>
       <c r="C156" s="5">
-        <f>IF(B156="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B156,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B156="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B156,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D156" s="43" t="n"/>
@@ -10659,7 +10971,7 @@
       <c r="A157" s="42" t="n"/>
       <c r="B157" s="43" t="n"/>
       <c r="C157" s="5">
-        <f>IF(B157="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B157,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B157="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B157,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D157" s="43" t="n"/>
@@ -10676,7 +10988,7 @@
       <c r="A158" s="42" t="n"/>
       <c r="B158" s="43" t="n"/>
       <c r="C158" s="5">
-        <f>IF(B158="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B158,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B158="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B158,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D158" s="43" t="n"/>
@@ -10693,7 +11005,7 @@
       <c r="A159" s="42" t="n"/>
       <c r="B159" s="43" t="n"/>
       <c r="C159" s="5">
-        <f>IF(B159="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B159,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B159="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B159,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D159" s="43" t="n"/>
@@ -10710,7 +11022,7 @@
       <c r="A160" s="42" t="n"/>
       <c r="B160" s="43" t="n"/>
       <c r="C160" s="5">
-        <f>IF(B160="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B160,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B160="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B160,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D160" s="43" t="n"/>
@@ -10727,7 +11039,7 @@
       <c r="A161" s="42" t="n"/>
       <c r="B161" s="43" t="n"/>
       <c r="C161" s="5">
-        <f>IF(B161="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B161,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B161="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B161,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D161" s="43" t="n"/>
@@ -10744,7 +11056,7 @@
       <c r="A162" s="42" t="n"/>
       <c r="B162" s="43" t="n"/>
       <c r="C162" s="5">
-        <f>IF(B162="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B162,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B162="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B162,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D162" s="43" t="n"/>
@@ -10761,7 +11073,7 @@
       <c r="A163" s="42" t="n"/>
       <c r="B163" s="43" t="n"/>
       <c r="C163" s="5">
-        <f>IF(B163="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B163,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B163="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B163,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D163" s="43" t="n"/>
@@ -10778,7 +11090,7 @@
       <c r="A164" s="42" t="n"/>
       <c r="B164" s="43" t="n"/>
       <c r="C164" s="5">
-        <f>IF(B164="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B164,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B164="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B164,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D164" s="43" t="n"/>
@@ -10795,7 +11107,7 @@
       <c r="A165" s="42" t="n"/>
       <c r="B165" s="43" t="n"/>
       <c r="C165" s="5">
-        <f>IF(B165="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B165,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B165="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B165,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D165" s="43" t="n"/>
@@ -10812,7 +11124,7 @@
       <c r="A166" s="42" t="n"/>
       <c r="B166" s="43" t="n"/>
       <c r="C166" s="5">
-        <f>IF(B166="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B166,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B166="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B166,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D166" s="43" t="n"/>
@@ -10829,7 +11141,7 @@
       <c r="A167" s="42" t="n"/>
       <c r="B167" s="43" t="n"/>
       <c r="C167" s="5">
-        <f>IF(B167="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B167,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B167="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B167,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D167" s="43" t="n"/>
@@ -10846,7 +11158,7 @@
       <c r="A168" s="42" t="n"/>
       <c r="B168" s="43" t="n"/>
       <c r="C168" s="5">
-        <f>IF(B168="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B168,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B168="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B168,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D168" s="43" t="n"/>
@@ -10863,7 +11175,7 @@
       <c r="A169" s="42" t="n"/>
       <c r="B169" s="43" t="n"/>
       <c r="C169" s="5">
-        <f>IF(B169="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B169,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B169="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B169,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D169" s="43" t="n"/>
@@ -10880,7 +11192,7 @@
       <c r="A170" s="42" t="n"/>
       <c r="B170" s="43" t="n"/>
       <c r="C170" s="5">
-        <f>IF(B170="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B170,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B170="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B170,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D170" s="43" t="n"/>
@@ -10897,7 +11209,7 @@
       <c r="A171" s="42" t="n"/>
       <c r="B171" s="43" t="n"/>
       <c r="C171" s="5">
-        <f>IF(B171="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B171,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B171="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B171,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D171" s="43" t="n"/>
@@ -10914,7 +11226,7 @@
       <c r="A172" s="42" t="n"/>
       <c r="B172" s="43" t="n"/>
       <c r="C172" s="5">
-        <f>IF(B172="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B172,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B172="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B172,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D172" s="43" t="n"/>
@@ -10931,7 +11243,7 @@
       <c r="A173" s="42" t="n"/>
       <c r="B173" s="43" t="n"/>
       <c r="C173" s="5">
-        <f>IF(B173="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B173,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B173="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B173,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D173" s="43" t="n"/>
@@ -10948,7 +11260,7 @@
       <c r="A174" s="42" t="n"/>
       <c r="B174" s="43" t="n"/>
       <c r="C174" s="5">
-        <f>IF(B174="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B174,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B174="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B174,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D174" s="43" t="n"/>
@@ -10965,7 +11277,7 @@
       <c r="A175" s="42" t="n"/>
       <c r="B175" s="43" t="n"/>
       <c r="C175" s="5">
-        <f>IF(B175="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B175,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B175="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B175,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D175" s="43" t="n"/>
@@ -10982,7 +11294,7 @@
       <c r="A176" s="42" t="n"/>
       <c r="B176" s="43" t="n"/>
       <c r="C176" s="5">
-        <f>IF(B176="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B176,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B176="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B176,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D176" s="43" t="n"/>
@@ -10999,7 +11311,7 @@
       <c r="A177" s="42" t="n"/>
       <c r="B177" s="43" t="n"/>
       <c r="C177" s="5">
-        <f>IF(B177="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B177,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B177="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B177,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D177" s="43" t="n"/>
@@ -11016,7 +11328,7 @@
       <c r="A178" s="42" t="n"/>
       <c r="B178" s="43" t="n"/>
       <c r="C178" s="5">
-        <f>IF(B178="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B178,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B178="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B178,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D178" s="43" t="n"/>
@@ -11033,7 +11345,7 @@
       <c r="A179" s="42" t="n"/>
       <c r="B179" s="43" t="n"/>
       <c r="C179" s="5">
-        <f>IF(B179="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B179,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B179="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B179,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D179" s="43" t="n"/>
@@ -11050,7 +11362,7 @@
       <c r="A180" s="42" t="n"/>
       <c r="B180" s="43" t="n"/>
       <c r="C180" s="5">
-        <f>IF(B180="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B180,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B180="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B180,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D180" s="43" t="n"/>
@@ -11067,7 +11379,7 @@
       <c r="A181" s="42" t="n"/>
       <c r="B181" s="43" t="n"/>
       <c r="C181" s="5">
-        <f>IF(B181="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B181,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B181="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B181,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D181" s="43" t="n"/>
@@ -11084,7 +11396,7 @@
       <c r="A182" s="42" t="n"/>
       <c r="B182" s="43" t="n"/>
       <c r="C182" s="5">
-        <f>IF(B182="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B182,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B182="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B182,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D182" s="43" t="n"/>
@@ -11101,7 +11413,7 @@
       <c r="A183" s="42" t="n"/>
       <c r="B183" s="43" t="n"/>
       <c r="C183" s="5">
-        <f>IF(B183="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B183,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B183="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B183,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D183" s="43" t="n"/>
@@ -11118,7 +11430,7 @@
       <c r="A184" s="42" t="n"/>
       <c r="B184" s="43" t="n"/>
       <c r="C184" s="5">
-        <f>IF(B184="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B184,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B184="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B184,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D184" s="43" t="n"/>
@@ -11135,7 +11447,7 @@
       <c r="A185" s="42" t="n"/>
       <c r="B185" s="43" t="n"/>
       <c r="C185" s="5">
-        <f>IF(B185="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B185,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B185="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B185,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D185" s="43" t="n"/>
@@ -11152,7 +11464,7 @@
       <c r="A186" s="42" t="n"/>
       <c r="B186" s="43" t="n"/>
       <c r="C186" s="5">
-        <f>IF(B186="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B186,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B186="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B186,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D186" s="43" t="n"/>
@@ -11169,7 +11481,7 @@
       <c r="A187" s="42" t="n"/>
       <c r="B187" s="43" t="n"/>
       <c r="C187" s="5">
-        <f>IF(B187="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B187,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B187="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B187,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D187" s="43" t="n"/>
@@ -11186,7 +11498,7 @@
       <c r="A188" s="42" t="n"/>
       <c r="B188" s="43" t="n"/>
       <c r="C188" s="5">
-        <f>IF(B188="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B188,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B188="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B188,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D188" s="43" t="n"/>
@@ -11203,7 +11515,7 @@
       <c r="A189" s="42" t="n"/>
       <c r="B189" s="43" t="n"/>
       <c r="C189" s="5">
-        <f>IF(B189="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B189,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B189="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B189,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D189" s="43" t="n"/>
@@ -11220,7 +11532,7 @@
       <c r="A190" s="42" t="n"/>
       <c r="B190" s="43" t="n"/>
       <c r="C190" s="5">
-        <f>IF(B190="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B190,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B190="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B190,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D190" s="43" t="n"/>
@@ -11237,7 +11549,7 @@
       <c r="A191" s="42" t="n"/>
       <c r="B191" s="43" t="n"/>
       <c r="C191" s="5">
-        <f>IF(B191="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B191,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B191="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B191,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D191" s="43" t="n"/>
@@ -11254,7 +11566,7 @@
       <c r="A192" s="42" t="n"/>
       <c r="B192" s="43" t="n"/>
       <c r="C192" s="5">
-        <f>IF(B192="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B192,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B192="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B192,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D192" s="43" t="n"/>
@@ -11271,7 +11583,7 @@
       <c r="A193" s="42" t="n"/>
       <c r="B193" s="43" t="n"/>
       <c r="C193" s="5">
-        <f>IF(B193="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B193,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B193="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B193,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D193" s="43" t="n"/>
@@ -11288,7 +11600,7 @@
       <c r="A194" s="42" t="n"/>
       <c r="B194" s="43" t="n"/>
       <c r="C194" s="5">
-        <f>IF(B194="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B194,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B194="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B194,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D194" s="43" t="n"/>
@@ -11305,7 +11617,7 @@
       <c r="A195" s="42" t="n"/>
       <c r="B195" s="43" t="n"/>
       <c r="C195" s="5">
-        <f>IF(B195="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B195,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B195="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B195,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D195" s="43" t="n"/>
@@ -11322,7 +11634,7 @@
       <c r="A196" s="42" t="n"/>
       <c r="B196" s="43" t="n"/>
       <c r="C196" s="5">
-        <f>IF(B196="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B196,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B196="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B196,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D196" s="43" t="n"/>
@@ -11339,7 +11651,7 @@
       <c r="A197" s="42" t="n"/>
       <c r="B197" s="43" t="n"/>
       <c r="C197" s="5">
-        <f>IF(B197="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B197,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B197="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B197,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D197" s="43" t="n"/>
@@ -11356,7 +11668,7 @@
       <c r="A198" s="42" t="n"/>
       <c r="B198" s="43" t="n"/>
       <c r="C198" s="5">
-        <f>IF(B198="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B198,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B198="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B198,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D198" s="43" t="n"/>
@@ -11373,7 +11685,7 @@
       <c r="A199" s="42" t="n"/>
       <c r="B199" s="43" t="n"/>
       <c r="C199" s="5">
-        <f>IF(B199="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B199,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B199="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B199,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D199" s="43" t="n"/>
@@ -11390,7 +11702,7 @@
       <c r="A200" s="42" t="n"/>
       <c r="B200" s="43" t="n"/>
       <c r="C200" s="5">
-        <f>IF(B200="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B200,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B200="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B200,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D200" s="43" t="n"/>
@@ -11407,7 +11719,7 @@
       <c r="A201" s="42" t="n"/>
       <c r="B201" s="43" t="n"/>
       <c r="C201" s="5">
-        <f>IF(B201="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B201,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B201="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B201,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D201" s="43" t="n"/>
@@ -11424,7 +11736,7 @@
       <c r="A202" s="42" t="n"/>
       <c r="B202" s="43" t="n"/>
       <c r="C202" s="5">
-        <f>IF(B202="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B202,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B202="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B202,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D202" s="43" t="n"/>
@@ -11441,7 +11753,7 @@
       <c r="A203" s="42" t="n"/>
       <c r="B203" s="43" t="n"/>
       <c r="C203" s="5">
-        <f>IF(B203="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B203,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B203="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B203,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D203" s="43" t="n"/>
@@ -11458,7 +11770,7 @@
       <c r="A204" s="42" t="n"/>
       <c r="B204" s="43" t="n"/>
       <c r="C204" s="5">
-        <f>IF(B204="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B204,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B204="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B204,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D204" s="43" t="n"/>
@@ -11475,7 +11787,7 @@
       <c r="A205" s="42" t="n"/>
       <c r="B205" s="43" t="n"/>
       <c r="C205" s="5">
-        <f>IF(B205="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B205,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B205="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B205,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D205" s="43" t="n"/>
@@ -11492,7 +11804,7 @@
       <c r="A206" s="42" t="n"/>
       <c r="B206" s="43" t="n"/>
       <c r="C206" s="5">
-        <f>IF(B206="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B206,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B206="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B206,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D206" s="43" t="n"/>
@@ -11509,7 +11821,7 @@
       <c r="A207" s="42" t="n"/>
       <c r="B207" s="43" t="n"/>
       <c r="C207" s="5">
-        <f>IF(B207="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B207,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B207="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B207,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D207" s="43" t="n"/>
@@ -11526,7 +11838,7 @@
       <c r="A208" s="42" t="n"/>
       <c r="B208" s="43" t="n"/>
       <c r="C208" s="5">
-        <f>IF(B208="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B208,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B208="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B208,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D208" s="43" t="n"/>
@@ -11543,7 +11855,7 @@
       <c r="A209" s="42" t="n"/>
       <c r="B209" s="43" t="n"/>
       <c r="C209" s="5">
-        <f>IF(B209="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B209,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B209="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B209,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D209" s="43" t="n"/>
@@ -11560,7 +11872,7 @@
       <c r="A210" s="42" t="n"/>
       <c r="B210" s="43" t="n"/>
       <c r="C210" s="5">
-        <f>IF(B210="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B210,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B210="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B210,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D210" s="43" t="n"/>
@@ -11577,7 +11889,7 @@
       <c r="A211" s="42" t="n"/>
       <c r="B211" s="43" t="n"/>
       <c r="C211" s="5">
-        <f>IF(B211="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B211,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B211="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B211,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D211" s="43" t="n"/>
@@ -11594,7 +11906,7 @@
       <c r="A212" s="42" t="n"/>
       <c r="B212" s="43" t="n"/>
       <c r="C212" s="5">
-        <f>IF(B212="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B212,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B212="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B212,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D212" s="43" t="n"/>
@@ -11611,7 +11923,7 @@
       <c r="A213" s="42" t="n"/>
       <c r="B213" s="43" t="n"/>
       <c r="C213" s="5">
-        <f>IF(B213="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B213,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B213="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B213,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D213" s="43" t="n"/>
@@ -11628,7 +11940,7 @@
       <c r="A214" s="42" t="n"/>
       <c r="B214" s="43" t="n"/>
       <c r="C214" s="5">
-        <f>IF(B214="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B214,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B214="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B214,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D214" s="43" t="n"/>
@@ -11645,7 +11957,7 @@
       <c r="A215" s="42" t="n"/>
       <c r="B215" s="43" t="n"/>
       <c r="C215" s="5">
-        <f>IF(B215="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B215,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B215="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B215,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D215" s="43" t="n"/>
@@ -11662,7 +11974,7 @@
       <c r="A216" s="42" t="n"/>
       <c r="B216" s="43" t="n"/>
       <c r="C216" s="5">
-        <f>IF(B216="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B216,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B216="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B216,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D216" s="43" t="n"/>
@@ -11679,7 +11991,7 @@
       <c r="A217" s="42" t="n"/>
       <c r="B217" s="43" t="n"/>
       <c r="C217" s="5">
-        <f>IF(B217="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B217,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B217="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B217,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D217" s="43" t="n"/>
@@ -11696,7 +12008,7 @@
       <c r="A218" s="42" t="n"/>
       <c r="B218" s="43" t="n"/>
       <c r="C218" s="5">
-        <f>IF(B218="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B218,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B218="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B218,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D218" s="43" t="n"/>
@@ -11713,7 +12025,7 @@
       <c r="A219" s="42" t="n"/>
       <c r="B219" s="43" t="n"/>
       <c r="C219" s="5">
-        <f>IF(B219="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B219,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B219="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B219,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D219" s="43" t="n"/>
@@ -11730,7 +12042,7 @@
       <c r="A220" s="42" t="n"/>
       <c r="B220" s="43" t="n"/>
       <c r="C220" s="5">
-        <f>IF(B220="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B220,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B220="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B220,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D220" s="43" t="n"/>
@@ -11747,7 +12059,7 @@
       <c r="A221" s="42" t="n"/>
       <c r="B221" s="43" t="n"/>
       <c r="C221" s="5">
-        <f>IF(B221="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B221,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B221="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B221,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D221" s="43" t="n"/>
@@ -11764,7 +12076,7 @@
       <c r="A222" s="42" t="n"/>
       <c r="B222" s="43" t="n"/>
       <c r="C222" s="5">
-        <f>IF(B222="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B222,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B222="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B222,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D222" s="43" t="n"/>
@@ -11781,7 +12093,7 @@
       <c r="A223" s="42" t="n"/>
       <c r="B223" s="43" t="n"/>
       <c r="C223" s="5">
-        <f>IF(B223="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B223,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B223="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B223,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D223" s="43" t="n"/>
@@ -11798,7 +12110,7 @@
       <c r="A224" s="42" t="n"/>
       <c r="B224" s="43" t="n"/>
       <c r="C224" s="5">
-        <f>IF(B224="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B224,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B224="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B224,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D224" s="43" t="n"/>
@@ -11815,7 +12127,7 @@
       <c r="A225" s="42" t="n"/>
       <c r="B225" s="43" t="n"/>
       <c r="C225" s="5">
-        <f>IF(B225="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B225,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B225="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B225,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D225" s="43" t="n"/>
@@ -11832,7 +12144,7 @@
       <c r="A226" s="42" t="n"/>
       <c r="B226" s="43" t="n"/>
       <c r="C226" s="5">
-        <f>IF(B226="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B226,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B226="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B226,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D226" s="43" t="n"/>
@@ -11849,7 +12161,7 @@
       <c r="A227" s="42" t="n"/>
       <c r="B227" s="43" t="n"/>
       <c r="C227" s="5">
-        <f>IF(B227="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B227,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B227="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B227,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D227" s="43" t="n"/>
@@ -11866,7 +12178,7 @@
       <c r="A228" s="42" t="n"/>
       <c r="B228" s="43" t="n"/>
       <c r="C228" s="5">
-        <f>IF(B228="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B228,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B228="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B228,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D228" s="43" t="n"/>
@@ -11883,7 +12195,7 @@
       <c r="A229" s="42" t="n"/>
       <c r="B229" s="43" t="n"/>
       <c r="C229" s="5">
-        <f>IF(B229="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B229,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B229="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B229,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D229" s="43" t="n"/>
@@ -11900,7 +12212,7 @@
       <c r="A230" s="42" t="n"/>
       <c r="B230" s="43" t="n"/>
       <c r="C230" s="5">
-        <f>IF(B230="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B230,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B230="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B230,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D230" s="43" t="n"/>
@@ -11917,7 +12229,7 @@
       <c r="A231" s="42" t="n"/>
       <c r="B231" s="43" t="n"/>
       <c r="C231" s="5">
-        <f>IF(B231="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B231,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B231="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B231,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D231" s="43" t="n"/>
@@ -11934,7 +12246,7 @@
       <c r="A232" s="42" t="n"/>
       <c r="B232" s="43" t="n"/>
       <c r="C232" s="5">
-        <f>IF(B232="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B232,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B232="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B232,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D232" s="43" t="n"/>
@@ -11951,7 +12263,7 @@
       <c r="A233" s="42" t="n"/>
       <c r="B233" s="43" t="n"/>
       <c r="C233" s="5">
-        <f>IF(B233="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B233,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B233="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B233,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D233" s="43" t="n"/>
@@ -11968,7 +12280,7 @@
       <c r="A234" s="42" t="n"/>
       <c r="B234" s="43" t="n"/>
       <c r="C234" s="5">
-        <f>IF(B234="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B234,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B234="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B234,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D234" s="43" t="n"/>
@@ -11985,7 +12297,7 @@
       <c r="A235" s="42" t="n"/>
       <c r="B235" s="43" t="n"/>
       <c r="C235" s="5">
-        <f>IF(B235="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B235,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B235="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B235,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D235" s="43" t="n"/>
@@ -12002,7 +12314,7 @@
       <c r="A236" s="42" t="n"/>
       <c r="B236" s="43" t="n"/>
       <c r="C236" s="5">
-        <f>IF(B236="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B236,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B236="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B236,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D236" s="43" t="n"/>
@@ -12019,7 +12331,7 @@
       <c r="A237" s="42" t="n"/>
       <c r="B237" s="43" t="n"/>
       <c r="C237" s="5">
-        <f>IF(B237="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B237,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B237="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B237,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D237" s="43" t="n"/>
@@ -12036,7 +12348,7 @@
       <c r="A238" s="42" t="n"/>
       <c r="B238" s="43" t="n"/>
       <c r="C238" s="5">
-        <f>IF(B238="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B238,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B238="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B238,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D238" s="43" t="n"/>
@@ -12053,7 +12365,7 @@
       <c r="A239" s="42" t="n"/>
       <c r="B239" s="43" t="n"/>
       <c r="C239" s="5">
-        <f>IF(B239="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B239,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B239="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B239,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D239" s="43" t="n"/>
@@ -12070,7 +12382,7 @@
       <c r="A240" s="42" t="n"/>
       <c r="B240" s="43" t="n"/>
       <c r="C240" s="5">
-        <f>IF(B240="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B240,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B240="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B240,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D240" s="43" t="n"/>
@@ -12087,7 +12399,7 @@
       <c r="A241" s="42" t="n"/>
       <c r="B241" s="43" t="n"/>
       <c r="C241" s="5">
-        <f>IF(B241="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B241,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B241="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B241,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D241" s="43" t="n"/>
@@ -12104,7 +12416,7 @@
       <c r="A242" s="42" t="n"/>
       <c r="B242" s="43" t="n"/>
       <c r="C242" s="5">
-        <f>IF(B242="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B242,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B242="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B242,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D242" s="43" t="n"/>
@@ -12121,7 +12433,7 @@
       <c r="A243" s="42" t="n"/>
       <c r="B243" s="43" t="n"/>
       <c r="C243" s="5">
-        <f>IF(B243="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B243,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B243="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B243,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D243" s="43" t="n"/>
@@ -12138,7 +12450,7 @@
       <c r="A244" s="42" t="n"/>
       <c r="B244" s="43" t="n"/>
       <c r="C244" s="5">
-        <f>IF(B244="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B244,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B244="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B244,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D244" s="43" t="n"/>
@@ -12155,7 +12467,7 @@
       <c r="A245" s="42" t="n"/>
       <c r="B245" s="43" t="n"/>
       <c r="C245" s="5">
-        <f>IF(B245="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B245,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B245="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B245,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D245" s="43" t="n"/>
@@ -12172,7 +12484,7 @@
       <c r="A246" s="42" t="n"/>
       <c r="B246" s="43" t="n"/>
       <c r="C246" s="5">
-        <f>IF(B246="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B246,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B246="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B246,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D246" s="43" t="n"/>
@@ -12189,7 +12501,7 @@
       <c r="A247" s="42" t="n"/>
       <c r="B247" s="43" t="n"/>
       <c r="C247" s="5">
-        <f>IF(B247="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B247,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B247="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B247,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D247" s="43" t="n"/>
@@ -12206,7 +12518,7 @@
       <c r="A248" s="42" t="n"/>
       <c r="B248" s="43" t="n"/>
       <c r="C248" s="5">
-        <f>IF(B248="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B248,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B248="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B248,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D248" s="43" t="n"/>
@@ -12223,7 +12535,7 @@
       <c r="A249" s="42" t="n"/>
       <c r="B249" s="43" t="n"/>
       <c r="C249" s="5">
-        <f>IF(B249="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B249,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B249="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B249,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D249" s="43" t="n"/>
@@ -12240,7 +12552,7 @@
       <c r="A250" s="42" t="n"/>
       <c r="B250" s="43" t="n"/>
       <c r="C250" s="5">
-        <f>IF(B250="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B250,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B250="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B250,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D250" s="43" t="n"/>
@@ -12257,7 +12569,7 @@
       <c r="A251" s="42" t="n"/>
       <c r="B251" s="43" t="n"/>
       <c r="C251" s="5">
-        <f>IF(B251="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B251,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B251="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B251,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D251" s="43" t="n"/>
@@ -12274,7 +12586,7 @@
       <c r="A252" s="42" t="n"/>
       <c r="B252" s="43" t="n"/>
       <c r="C252" s="5">
-        <f>IF(B252="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B252,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B252="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B252,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D252" s="43" t="n"/>
@@ -12291,7 +12603,7 @@
       <c r="A253" s="42" t="n"/>
       <c r="B253" s="43" t="n"/>
       <c r="C253" s="5">
-        <f>IF(B253="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B253,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B253="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B253,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D253" s="43" t="n"/>
@@ -12308,7 +12620,7 @@
       <c r="A254" s="42" t="n"/>
       <c r="B254" s="43" t="n"/>
       <c r="C254" s="5">
-        <f>IF(B254="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B254,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B254="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B254,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D254" s="43" t="n"/>
@@ -12325,7 +12637,7 @@
       <c r="A255" s="42" t="n"/>
       <c r="B255" s="43" t="n"/>
       <c r="C255" s="5">
-        <f>IF(B255="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B255,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B255="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B255,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D255" s="43" t="n"/>
@@ -12342,7 +12654,7 @@
       <c r="A256" s="42" t="n"/>
       <c r="B256" s="43" t="n"/>
       <c r="C256" s="5">
-        <f>IF(B256="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B256,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B256="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B256,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D256" s="43" t="n"/>
@@ -12359,7 +12671,7 @@
       <c r="A257" s="42" t="n"/>
       <c r="B257" s="43" t="n"/>
       <c r="C257" s="5">
-        <f>IF(B257="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B257,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B257="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B257,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D257" s="43" t="n"/>
@@ -12376,7 +12688,7 @@
       <c r="A258" s="42" t="n"/>
       <c r="B258" s="43" t="n"/>
       <c r="C258" s="5">
-        <f>IF(B258="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B258,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B258="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B258,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D258" s="43" t="n"/>
@@ -12393,7 +12705,7 @@
       <c r="A259" s="42" t="n"/>
       <c r="B259" s="43" t="n"/>
       <c r="C259" s="5">
-        <f>IF(B259="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B259,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B259="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B259,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D259" s="43" t="n"/>
@@ -12410,7 +12722,7 @@
       <c r="A260" s="42" t="n"/>
       <c r="B260" s="43" t="n"/>
       <c r="C260" s="5">
-        <f>IF(B260="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B260,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B260="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B260,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D260" s="43" t="n"/>
@@ -12427,7 +12739,7 @@
       <c r="A261" s="42" t="n"/>
       <c r="B261" s="43" t="n"/>
       <c r="C261" s="5">
-        <f>IF(B261="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B261,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B261="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B261,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D261" s="43" t="n"/>
@@ -12444,7 +12756,7 @@
       <c r="A262" s="42" t="n"/>
       <c r="B262" s="43" t="n"/>
       <c r="C262" s="5">
-        <f>IF(B262="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B262,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B262="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B262,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D262" s="43" t="n"/>
@@ -12461,7 +12773,7 @@
       <c r="A263" s="42" t="n"/>
       <c r="B263" s="43" t="n"/>
       <c r="C263" s="5">
-        <f>IF(B263="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B263,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B263="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B263,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D263" s="43" t="n"/>
@@ -12478,7 +12790,7 @@
       <c r="A264" s="42" t="n"/>
       <c r="B264" s="43" t="n"/>
       <c r="C264" s="5">
-        <f>IF(B264="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B264,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B264="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B264,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D264" s="43" t="n"/>
@@ -12495,7 +12807,7 @@
       <c r="A265" s="42" t="n"/>
       <c r="B265" s="43" t="n"/>
       <c r="C265" s="5">
-        <f>IF(B265="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B265,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B265="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B265,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D265" s="43" t="n"/>
@@ -12512,7 +12824,7 @@
       <c r="A266" s="42" t="n"/>
       <c r="B266" s="43" t="n"/>
       <c r="C266" s="5">
-        <f>IF(B266="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B266,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B266="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B266,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D266" s="43" t="n"/>
@@ -12529,7 +12841,7 @@
       <c r="A267" s="42" t="n"/>
       <c r="B267" s="43" t="n"/>
       <c r="C267" s="5">
-        <f>IF(B267="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B267,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B267="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B267,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D267" s="43" t="n"/>
@@ -12546,7 +12858,7 @@
       <c r="A268" s="42" t="n"/>
       <c r="B268" s="43" t="n"/>
       <c r="C268" s="5">
-        <f>IF(B268="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B268,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B268="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B268,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D268" s="43" t="n"/>
@@ -12563,7 +12875,7 @@
       <c r="A269" s="42" t="n"/>
       <c r="B269" s="43" t="n"/>
       <c r="C269" s="5">
-        <f>IF(B269="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B269,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B269="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B269,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D269" s="43" t="n"/>
@@ -12580,7 +12892,7 @@
       <c r="A270" s="42" t="n"/>
       <c r="B270" s="43" t="n"/>
       <c r="C270" s="5">
-        <f>IF(B270="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B270,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B270="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B270,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D270" s="43" t="n"/>
@@ -12597,7 +12909,7 @@
       <c r="A271" s="42" t="n"/>
       <c r="B271" s="43" t="n"/>
       <c r="C271" s="5">
-        <f>IF(B271="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B271,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B271="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B271,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D271" s="43" t="n"/>
@@ -12614,7 +12926,7 @@
       <c r="A272" s="42" t="n"/>
       <c r="B272" s="43" t="n"/>
       <c r="C272" s="5">
-        <f>IF(B272="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B272,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B272="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B272,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D272" s="43" t="n"/>
@@ -12631,7 +12943,7 @@
       <c r="A273" s="42" t="n"/>
       <c r="B273" s="43" t="n"/>
       <c r="C273" s="5">
-        <f>IF(B273="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B273,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B273="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B273,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D273" s="43" t="n"/>
@@ -12648,7 +12960,7 @@
       <c r="A274" s="42" t="n"/>
       <c r="B274" s="43" t="n"/>
       <c r="C274" s="5">
-        <f>IF(B274="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B274,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B274="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B274,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D274" s="43" t="n"/>
@@ -12665,7 +12977,7 @@
       <c r="A275" s="42" t="n"/>
       <c r="B275" s="43" t="n"/>
       <c r="C275" s="5">
-        <f>IF(B275="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B275,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B275="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B275,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D275" s="43" t="n"/>
@@ -12682,7 +12994,7 @@
       <c r="A276" s="42" t="n"/>
       <c r="B276" s="43" t="n"/>
       <c r="C276" s="5">
-        <f>IF(B276="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B276,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B276="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B276,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D276" s="43" t="n"/>
@@ -12699,7 +13011,7 @@
       <c r="A277" s="42" t="n"/>
       <c r="B277" s="43" t="n"/>
       <c r="C277" s="5">
-        <f>IF(B277="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B277,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B277="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B277,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D277" s="43" t="n"/>
@@ -12716,7 +13028,7 @@
       <c r="A278" s="42" t="n"/>
       <c r="B278" s="43" t="n"/>
       <c r="C278" s="5">
-        <f>IF(B278="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B278,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B278="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B278,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D278" s="43" t="n"/>
@@ -12733,7 +13045,7 @@
       <c r="A279" s="42" t="n"/>
       <c r="B279" s="43" t="n"/>
       <c r="C279" s="5">
-        <f>IF(B279="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B279,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B279="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B279,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D279" s="43" t="n"/>
@@ -12750,7 +13062,7 @@
       <c r="A280" s="42" t="n"/>
       <c r="B280" s="43" t="n"/>
       <c r="C280" s="5">
-        <f>IF(B280="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B280,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B280="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B280,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D280" s="43" t="n"/>
@@ -12767,7 +13079,7 @@
       <c r="A281" s="42" t="n"/>
       <c r="B281" s="43" t="n"/>
       <c r="C281" s="5">
-        <f>IF(B281="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B281,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B281="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B281,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D281" s="43" t="n"/>
@@ -12784,7 +13096,7 @@
       <c r="A282" s="42" t="n"/>
       <c r="B282" s="43" t="n"/>
       <c r="C282" s="5">
-        <f>IF(B282="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B282,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B282="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B282,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D282" s="43" t="n"/>
@@ -12801,7 +13113,7 @@
       <c r="A283" s="42" t="n"/>
       <c r="B283" s="43" t="n"/>
       <c r="C283" s="5">
-        <f>IF(B283="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B283,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B283="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B283,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D283" s="43" t="n"/>
@@ -12818,7 +13130,7 @@
       <c r="A284" s="42" t="n"/>
       <c r="B284" s="43" t="n"/>
       <c r="C284" s="5">
-        <f>IF(B284="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B284,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B284="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B284,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D284" s="43" t="n"/>
@@ -12835,7 +13147,7 @@
       <c r="A285" s="42" t="n"/>
       <c r="B285" s="43" t="n"/>
       <c r="C285" s="5">
-        <f>IF(B285="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B285,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B285="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B285,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D285" s="43" t="n"/>
@@ -12852,7 +13164,7 @@
       <c r="A286" s="42" t="n"/>
       <c r="B286" s="43" t="n"/>
       <c r="C286" s="5">
-        <f>IF(B286="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B286,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B286="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B286,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D286" s="43" t="n"/>
@@ -12869,7 +13181,7 @@
       <c r="A287" s="42" t="n"/>
       <c r="B287" s="43" t="n"/>
       <c r="C287" s="5">
-        <f>IF(B287="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B287,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B287="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B287,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D287" s="43" t="n"/>
@@ -12886,7 +13198,7 @@
       <c r="A288" s="42" t="n"/>
       <c r="B288" s="43" t="n"/>
       <c r="C288" s="5">
-        <f>IF(B288="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B288,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B288="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B288,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D288" s="43" t="n"/>
@@ -12903,7 +13215,7 @@
       <c r="A289" s="42" t="n"/>
       <c r="B289" s="43" t="n"/>
       <c r="C289" s="5">
-        <f>IF(B289="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B289,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B289="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B289,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D289" s="43" t="n"/>
@@ -12920,7 +13232,7 @@
       <c r="A290" s="42" t="n"/>
       <c r="B290" s="43" t="n"/>
       <c r="C290" s="5">
-        <f>IF(B290="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B290,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B290="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B290,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D290" s="43" t="n"/>
@@ -12937,7 +13249,7 @@
       <c r="A291" s="42" t="n"/>
       <c r="B291" s="43" t="n"/>
       <c r="C291" s="5">
-        <f>IF(B291="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B291,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B291="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B291,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D291" s="43" t="n"/>
@@ -12954,7 +13266,7 @@
       <c r="A292" s="42" t="n"/>
       <c r="B292" s="43" t="n"/>
       <c r="C292" s="5">
-        <f>IF(B292="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B292,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B292="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B292,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D292" s="43" t="n"/>
@@ -12971,7 +13283,7 @@
       <c r="A293" s="42" t="n"/>
       <c r="B293" s="43" t="n"/>
       <c r="C293" s="5">
-        <f>IF(B293="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B293,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B293="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B293,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D293" s="43" t="n"/>
@@ -12988,7 +13300,7 @@
       <c r="A294" s="42" t="n"/>
       <c r="B294" s="43" t="n"/>
       <c r="C294" s="5">
-        <f>IF(B294="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B294,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B294="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B294,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D294" s="43" t="n"/>
@@ -13005,7 +13317,7 @@
       <c r="A295" s="42" t="n"/>
       <c r="B295" s="43" t="n"/>
       <c r="C295" s="5">
-        <f>IF(B295="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B295,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B295="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B295,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D295" s="43" t="n"/>
@@ -13022,7 +13334,7 @@
       <c r="A296" s="42" t="n"/>
       <c r="B296" s="43" t="n"/>
       <c r="C296" s="5">
-        <f>IF(B296="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B296,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B296="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B296,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D296" s="43" t="n"/>
@@ -13039,7 +13351,7 @@
       <c r="A297" s="42" t="n"/>
       <c r="B297" s="43" t="n"/>
       <c r="C297" s="5">
-        <f>IF(B297="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B297,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B297="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B297,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D297" s="43" t="n"/>
@@ -13056,7 +13368,7 @@
       <c r="A298" s="42" t="n"/>
       <c r="B298" s="43" t="n"/>
       <c r="C298" s="5">
-        <f>IF(B298="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B298,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B298="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B298,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D298" s="43" t="n"/>
@@ -13073,7 +13385,7 @@
       <c r="A299" s="42" t="n"/>
       <c r="B299" s="43" t="n"/>
       <c r="C299" s="5">
-        <f>IF(B299="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B299,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B299="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B299,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D299" s="43" t="n"/>
@@ -13090,7 +13402,7 @@
       <c r="A300" s="42" t="n"/>
       <c r="B300" s="43" t="n"/>
       <c r="C300" s="5">
-        <f>IF(B300="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B300,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B300="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B300,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D300" s="43" t="n"/>
@@ -13107,7 +13419,7 @@
       <c r="A301" s="42" t="n"/>
       <c r="B301" s="43" t="n"/>
       <c r="C301" s="5">
-        <f>IF(B301="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B301,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B301="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B301,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D301" s="43" t="n"/>
@@ -13124,7 +13436,7 @@
       <c r="A302" s="42" t="n"/>
       <c r="B302" s="43" t="n"/>
       <c r="C302" s="5">
-        <f>IF(B302="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B302,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B302="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B302,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D302" s="43" t="n"/>
@@ -13141,7 +13453,7 @@
       <c r="A303" s="42" t="n"/>
       <c r="B303" s="43" t="n"/>
       <c r="C303" s="5">
-        <f>IF(B303="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B303,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B303="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B303,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D303" s="43" t="n"/>
@@ -13158,7 +13470,7 @@
       <c r="A304" s="42" t="n"/>
       <c r="B304" s="43" t="n"/>
       <c r="C304" s="5">
-        <f>IF(B304="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B304,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B304="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B304,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D304" s="43" t="n"/>
@@ -13175,7 +13487,7 @@
       <c r="A305" s="42" t="n"/>
       <c r="B305" s="43" t="n"/>
       <c r="C305" s="5">
-        <f>IF(B305="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B305,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B305="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B305,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D305" s="43" t="n"/>
@@ -13192,7 +13504,7 @@
       <c r="A306" s="42" t="n"/>
       <c r="B306" s="43" t="n"/>
       <c r="C306" s="5">
-        <f>IF(B306="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B306,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B306="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B306,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D306" s="43" t="n"/>
@@ -13209,7 +13521,7 @@
       <c r="A307" s="42" t="n"/>
       <c r="B307" s="43" t="n"/>
       <c r="C307" s="5">
-        <f>IF(B307="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B307,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B307="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B307,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D307" s="43" t="n"/>
@@ -13226,7 +13538,7 @@
       <c r="A308" s="42" t="n"/>
       <c r="B308" s="43" t="n"/>
       <c r="C308" s="5">
-        <f>IF(B308="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B308,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B308="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B308,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D308" s="43" t="n"/>
@@ -13243,7 +13555,7 @@
       <c r="A309" s="42" t="n"/>
       <c r="B309" s="43" t="n"/>
       <c r="C309" s="5">
-        <f>IF(B309="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B309,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B309="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B309,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D309" s="43" t="n"/>
@@ -13260,7 +13572,7 @@
       <c r="A310" s="42" t="n"/>
       <c r="B310" s="43" t="n"/>
       <c r="C310" s="5">
-        <f>IF(B310="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B310,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B310="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B310,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D310" s="43" t="n"/>
@@ -13277,7 +13589,7 @@
       <c r="A311" s="42" t="n"/>
       <c r="B311" s="43" t="n"/>
       <c r="C311" s="5">
-        <f>IF(B311="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B311,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B311="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B311,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D311" s="43" t="n"/>
@@ -13294,7 +13606,7 @@
       <c r="A312" s="42" t="n"/>
       <c r="B312" s="43" t="n"/>
       <c r="C312" s="5">
-        <f>IF(B312="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B312,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B312="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B312,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D312" s="43" t="n"/>
@@ -13311,7 +13623,7 @@
       <c r="A313" s="42" t="n"/>
       <c r="B313" s="43" t="n"/>
       <c r="C313" s="5">
-        <f>IF(B313="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B313,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B313="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B313,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D313" s="43" t="n"/>
@@ -13328,7 +13640,7 @@
       <c r="A314" s="42" t="n"/>
       <c r="B314" s="43" t="n"/>
       <c r="C314" s="5">
-        <f>IF(B314="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B314,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B314="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B314,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D314" s="43" t="n"/>
@@ -13345,7 +13657,7 @@
       <c r="A315" s="42" t="n"/>
       <c r="B315" s="43" t="n"/>
       <c r="C315" s="5">
-        <f>IF(B315="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B315,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B315="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B315,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D315" s="43" t="n"/>
@@ -13362,7 +13674,7 @@
       <c r="A316" s="42" t="n"/>
       <c r="B316" s="43" t="n"/>
       <c r="C316" s="5">
-        <f>IF(B316="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B316,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B316="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B316,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D316" s="43" t="n"/>
@@ -13379,7 +13691,7 @@
       <c r="A317" s="42" t="n"/>
       <c r="B317" s="43" t="n"/>
       <c r="C317" s="5">
-        <f>IF(B317="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B317,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B317="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B317,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D317" s="43" t="n"/>
@@ -13396,7 +13708,7 @@
       <c r="A318" s="42" t="n"/>
       <c r="B318" s="43" t="n"/>
       <c r="C318" s="5">
-        <f>IF(B318="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B318,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B318="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B318,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D318" s="43" t="n"/>
@@ -13413,7 +13725,7 @@
       <c r="A319" s="42" t="n"/>
       <c r="B319" s="43" t="n"/>
       <c r="C319" s="5">
-        <f>IF(B319="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B319,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B319="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B319,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D319" s="43" t="n"/>
@@ -13430,7 +13742,7 @@
       <c r="A320" s="42" t="n"/>
       <c r="B320" s="43" t="n"/>
       <c r="C320" s="5">
-        <f>IF(B320="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B320,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B320="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B320,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D320" s="43" t="n"/>
@@ -13447,7 +13759,7 @@
       <c r="A321" s="42" t="n"/>
       <c r="B321" s="43" t="n"/>
       <c r="C321" s="5">
-        <f>IF(B321="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B321,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B321="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B321,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D321" s="43" t="n"/>
@@ -13464,7 +13776,7 @@
       <c r="A322" s="42" t="n"/>
       <c r="B322" s="43" t="n"/>
       <c r="C322" s="5">
-        <f>IF(B322="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B322,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B322="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B322,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D322" s="43" t="n"/>
@@ -13481,7 +13793,7 @@
       <c r="A323" s="42" t="n"/>
       <c r="B323" s="43" t="n"/>
       <c r="C323" s="5">
-        <f>IF(B323="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B323,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B323="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B323,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D323" s="43" t="n"/>
@@ -13498,7 +13810,7 @@
       <c r="A324" s="42" t="n"/>
       <c r="B324" s="43" t="n"/>
       <c r="C324" s="5">
-        <f>IF(B324="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B324,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B324="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B324,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D324" s="43" t="n"/>
@@ -13515,7 +13827,7 @@
       <c r="A325" s="42" t="n"/>
       <c r="B325" s="43" t="n"/>
       <c r="C325" s="5">
-        <f>IF(B325="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B325,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B325="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B325,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D325" s="43" t="n"/>
@@ -13532,7 +13844,7 @@
       <c r="A326" s="42" t="n"/>
       <c r="B326" s="43" t="n"/>
       <c r="C326" s="5">
-        <f>IF(B326="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B326,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B326="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B326,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D326" s="43" t="n"/>
@@ -13549,7 +13861,7 @@
       <c r="A327" s="42" t="n"/>
       <c r="B327" s="43" t="n"/>
       <c r="C327" s="5">
-        <f>IF(B327="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B327,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B327="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B327,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D327" s="43" t="n"/>
@@ -13566,7 +13878,7 @@
       <c r="A328" s="42" t="n"/>
       <c r="B328" s="43" t="n"/>
       <c r="C328" s="5">
-        <f>IF(B328="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B328,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B328="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B328,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D328" s="43" t="n"/>
@@ -13583,7 +13895,7 @@
       <c r="A329" s="42" t="n"/>
       <c r="B329" s="43" t="n"/>
       <c r="C329" s="5">
-        <f>IF(B329="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B329,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B329="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B329,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D329" s="43" t="n"/>
@@ -13600,7 +13912,7 @@
       <c r="A330" s="42" t="n"/>
       <c r="B330" s="43" t="n"/>
       <c r="C330" s="5">
-        <f>IF(B330="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B330,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B330="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B330,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D330" s="43" t="n"/>
@@ -13617,7 +13929,7 @@
       <c r="A331" s="42" t="n"/>
       <c r="B331" s="43" t="n"/>
       <c r="C331" s="5">
-        <f>IF(B331="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B331,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B331="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B331,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D331" s="43" t="n"/>
@@ -13634,7 +13946,7 @@
       <c r="A332" s="42" t="n"/>
       <c r="B332" s="43" t="n"/>
       <c r="C332" s="5">
-        <f>IF(B332="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B332,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B332="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B332,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D332" s="43" t="n"/>
@@ -13651,7 +13963,7 @@
       <c r="A333" s="42" t="n"/>
       <c r="B333" s="43" t="n"/>
       <c r="C333" s="5">
-        <f>IF(B333="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B333,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B333="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B333,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D333" s="43" t="n"/>
@@ -13668,7 +13980,7 @@
       <c r="A334" s="42" t="n"/>
       <c r="B334" s="43" t="n"/>
       <c r="C334" s="5">
-        <f>IF(B334="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B334,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B334="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B334,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D334" s="43" t="n"/>
@@ -13685,7 +13997,7 @@
       <c r="A335" s="42" t="n"/>
       <c r="B335" s="43" t="n"/>
       <c r="C335" s="5">
-        <f>IF(B335="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B335,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B335="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B335,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D335" s="43" t="n"/>
@@ -13702,7 +14014,7 @@
       <c r="A336" s="42" t="n"/>
       <c r="B336" s="43" t="n"/>
       <c r="C336" s="5">
-        <f>IF(B336="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B336,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B336="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B336,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D336" s="43" t="n"/>
@@ -13719,7 +14031,7 @@
       <c r="A337" s="42" t="n"/>
       <c r="B337" s="43" t="n"/>
       <c r="C337" s="5">
-        <f>IF(B337="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B337,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B337="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B337,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D337" s="43" t="n"/>
@@ -13736,7 +14048,7 @@
       <c r="A338" s="42" t="n"/>
       <c r="B338" s="43" t="n"/>
       <c r="C338" s="5">
-        <f>IF(B338="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B338,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B338="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B338,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D338" s="43" t="n"/>
@@ -13753,7 +14065,7 @@
       <c r="A339" s="42" t="n"/>
       <c r="B339" s="43" t="n"/>
       <c r="C339" s="5">
-        <f>IF(B339="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B339,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B339="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B339,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D339" s="43" t="n"/>
@@ -13770,7 +14082,7 @@
       <c r="A340" s="42" t="n"/>
       <c r="B340" s="43" t="n"/>
       <c r="C340" s="5">
-        <f>IF(B340="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B340,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B340="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B340,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D340" s="43" t="n"/>
@@ -13787,7 +14099,7 @@
       <c r="A341" s="42" t="n"/>
       <c r="B341" s="43" t="n"/>
       <c r="C341" s="5">
-        <f>IF(B341="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B341,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B341="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B341,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D341" s="43" t="n"/>
@@ -13804,7 +14116,7 @@
       <c r="A342" s="42" t="n"/>
       <c r="B342" s="43" t="n"/>
       <c r="C342" s="5">
-        <f>IF(B342="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B342,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B342="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B342,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D342" s="43" t="n"/>
@@ -13821,7 +14133,7 @@
       <c r="A343" s="42" t="n"/>
       <c r="B343" s="43" t="n"/>
       <c r="C343" s="5">
-        <f>IF(B343="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B343,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B343="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B343,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D343" s="43" t="n"/>
@@ -13838,7 +14150,7 @@
       <c r="A344" s="42" t="n"/>
       <c r="B344" s="43" t="n"/>
       <c r="C344" s="5">
-        <f>IF(B344="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B344,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B344="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B344,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D344" s="43" t="n"/>
@@ -13855,7 +14167,7 @@
       <c r="A345" s="42" t="n"/>
       <c r="B345" s="43" t="n"/>
       <c r="C345" s="5">
-        <f>IF(B345="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B345,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B345="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B345,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D345" s="43" t="n"/>
@@ -13872,7 +14184,7 @@
       <c r="A346" s="42" t="n"/>
       <c r="B346" s="43" t="n"/>
       <c r="C346" s="5">
-        <f>IF(B346="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B346,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B346="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B346,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D346" s="43" t="n"/>
@@ -13889,7 +14201,7 @@
       <c r="A347" s="42" t="n"/>
       <c r="B347" s="43" t="n"/>
       <c r="C347" s="5">
-        <f>IF(B347="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B347,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B347="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B347,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D347" s="43" t="n"/>
@@ -13906,7 +14218,7 @@
       <c r="A348" s="42" t="n"/>
       <c r="B348" s="43" t="n"/>
       <c r="C348" s="5">
-        <f>IF(B348="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B348,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B348="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B348,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D348" s="43" t="n"/>
@@ -13923,7 +14235,7 @@
       <c r="A349" s="42" t="n"/>
       <c r="B349" s="43" t="n"/>
       <c r="C349" s="5">
-        <f>IF(B349="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B349,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B349="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B349,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D349" s="43" t="n"/>
@@ -13940,7 +14252,7 @@
       <c r="A350" s="42" t="n"/>
       <c r="B350" s="43" t="n"/>
       <c r="C350" s="5">
-        <f>IF(B350="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B350,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B350="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B350,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D350" s="43" t="n"/>
@@ -13957,7 +14269,7 @@
       <c r="A351" s="42" t="n"/>
       <c r="B351" s="43" t="n"/>
       <c r="C351" s="5">
-        <f>IF(B351="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B351,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B351="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B351,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D351" s="43" t="n"/>
@@ -13974,7 +14286,7 @@
       <c r="A352" s="42" t="n"/>
       <c r="B352" s="43" t="n"/>
       <c r="C352" s="5">
-        <f>IF(B352="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B352,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B352="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B352,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D352" s="43" t="n"/>
@@ -13991,7 +14303,7 @@
       <c r="A353" s="42" t="n"/>
       <c r="B353" s="43" t="n"/>
       <c r="C353" s="5">
-        <f>IF(B353="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B353,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B353="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B353,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D353" s="43" t="n"/>
@@ -14008,7 +14320,7 @@
       <c r="A354" s="42" t="n"/>
       <c r="B354" s="43" t="n"/>
       <c r="C354" s="5">
-        <f>IF(B354="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B354,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B354="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B354,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D354" s="43" t="n"/>
@@ -14025,7 +14337,7 @@
       <c r="A355" s="42" t="n"/>
       <c r="B355" s="43" t="n"/>
       <c r="C355" s="5">
-        <f>IF(B355="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B355,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B355="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B355,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D355" s="43" t="n"/>
@@ -14042,7 +14354,7 @@
       <c r="A356" s="42" t="n"/>
       <c r="B356" s="43" t="n"/>
       <c r="C356" s="5">
-        <f>IF(B356="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B356,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B356="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B356,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D356" s="43" t="n"/>
@@ -14059,7 +14371,7 @@
       <c r="A357" s="42" t="n"/>
       <c r="B357" s="43" t="n"/>
       <c r="C357" s="5">
-        <f>IF(B357="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B357,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B357="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B357,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D357" s="43" t="n"/>
@@ -14076,7 +14388,7 @@
       <c r="A358" s="42" t="n"/>
       <c r="B358" s="43" t="n"/>
       <c r="C358" s="5">
-        <f>IF(B358="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B358,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B358="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B358,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D358" s="43" t="n"/>
@@ -14093,7 +14405,7 @@
       <c r="A359" s="42" t="n"/>
       <c r="B359" s="43" t="n"/>
       <c r="C359" s="5">
-        <f>IF(B359="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B359,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B359="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B359,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D359" s="43" t="n"/>
@@ -14110,7 +14422,7 @@
       <c r="A360" s="42" t="n"/>
       <c r="B360" s="43" t="n"/>
       <c r="C360" s="5">
-        <f>IF(B360="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B360,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B360="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B360,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D360" s="43" t="n"/>
@@ -14127,7 +14439,7 @@
       <c r="A361" s="42" t="n"/>
       <c r="B361" s="43" t="n"/>
       <c r="C361" s="5">
-        <f>IF(B361="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B361,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B361="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B361,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D361" s="43" t="n"/>
@@ -14144,7 +14456,7 @@
       <c r="A362" s="42" t="n"/>
       <c r="B362" s="43" t="n"/>
       <c r="C362" s="5">
-        <f>IF(B362="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B362,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B362="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B362,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D362" s="43" t="n"/>
@@ -14161,7 +14473,7 @@
       <c r="A363" s="42" t="n"/>
       <c r="B363" s="43" t="n"/>
       <c r="C363" s="5">
-        <f>IF(B363="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B363,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B363="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B363,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D363" s="43" t="n"/>
@@ -14178,7 +14490,7 @@
       <c r="A364" s="42" t="n"/>
       <c r="B364" s="43" t="n"/>
       <c r="C364" s="5">
-        <f>IF(B364="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B364,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B364="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B364,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D364" s="43" t="n"/>
@@ -14195,7 +14507,7 @@
       <c r="A365" s="42" t="n"/>
       <c r="B365" s="43" t="n"/>
       <c r="C365" s="5">
-        <f>IF(B365="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B365,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B365="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B365,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D365" s="43" t="n"/>
@@ -14212,7 +14524,7 @@
       <c r="A366" s="42" t="n"/>
       <c r="B366" s="43" t="n"/>
       <c r="C366" s="5">
-        <f>IF(B366="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B366,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B366="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B366,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D366" s="43" t="n"/>
@@ -14229,7 +14541,7 @@
       <c r="A367" s="42" t="n"/>
       <c r="B367" s="43" t="n"/>
       <c r="C367" s="5">
-        <f>IF(B367="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B367,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B367="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B367,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D367" s="43" t="n"/>
@@ -14246,7 +14558,7 @@
       <c r="A368" s="42" t="n"/>
       <c r="B368" s="43" t="n"/>
       <c r="C368" s="5">
-        <f>IF(B368="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B368,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B368="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B368,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D368" s="43" t="n"/>
@@ -14263,7 +14575,7 @@
       <c r="A369" s="42" t="n"/>
       <c r="B369" s="43" t="n"/>
       <c r="C369" s="5">
-        <f>IF(B369="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B369,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B369="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B369,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D369" s="43" t="n"/>
@@ -14280,7 +14592,7 @@
       <c r="A370" s="42" t="n"/>
       <c r="B370" s="43" t="n"/>
       <c r="C370" s="5">
-        <f>IF(B370="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B370,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B370="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B370,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D370" s="43" t="n"/>
@@ -14297,7 +14609,7 @@
       <c r="A371" s="42" t="n"/>
       <c r="B371" s="43" t="n"/>
       <c r="C371" s="5">
-        <f>IF(B371="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B371,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B371="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B371,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D371" s="43" t="n"/>
@@ -14314,7 +14626,7 @@
       <c r="A372" s="42" t="n"/>
       <c r="B372" s="43" t="n"/>
       <c r="C372" s="5">
-        <f>IF(B372="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B372,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B372="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B372,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D372" s="43" t="n"/>
@@ -14331,7 +14643,7 @@
       <c r="A373" s="42" t="n"/>
       <c r="B373" s="43" t="n"/>
       <c r="C373" s="5">
-        <f>IF(B373="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B373,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B373="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B373,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D373" s="43" t="n"/>
@@ -14348,7 +14660,7 @@
       <c r="A374" s="42" t="n"/>
       <c r="B374" s="43" t="n"/>
       <c r="C374" s="5">
-        <f>IF(B374="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B374,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B374="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B374,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D374" s="43" t="n"/>
@@ -14365,7 +14677,7 @@
       <c r="A375" s="42" t="n"/>
       <c r="B375" s="43" t="n"/>
       <c r="C375" s="5">
-        <f>IF(B375="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B375,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B375="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B375,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D375" s="43" t="n"/>
@@ -14382,7 +14694,7 @@
       <c r="A376" s="42" t="n"/>
       <c r="B376" s="43" t="n"/>
       <c r="C376" s="5">
-        <f>IF(B376="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B376,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B376="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B376,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D376" s="43" t="n"/>
@@ -14399,7 +14711,7 @@
       <c r="A377" s="42" t="n"/>
       <c r="B377" s="43" t="n"/>
       <c r="C377" s="5">
-        <f>IF(B377="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B377,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B377="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B377,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D377" s="43" t="n"/>
@@ -14416,7 +14728,7 @@
       <c r="A378" s="42" t="n"/>
       <c r="B378" s="43" t="n"/>
       <c r="C378" s="5">
-        <f>IF(B378="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B378,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B378="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B378,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D378" s="43" t="n"/>
@@ -14433,7 +14745,7 @@
       <c r="A379" s="42" t="n"/>
       <c r="B379" s="43" t="n"/>
       <c r="C379" s="5">
-        <f>IF(B379="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B379,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B379="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B379,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D379" s="43" t="n"/>
@@ -14450,7 +14762,7 @@
       <c r="A380" s="42" t="n"/>
       <c r="B380" s="43" t="n"/>
       <c r="C380" s="5">
-        <f>IF(B380="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B380,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B380="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B380,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D380" s="43" t="n"/>
@@ -14467,7 +14779,7 @@
       <c r="A381" s="42" t="n"/>
       <c r="B381" s="43" t="n"/>
       <c r="C381" s="5">
-        <f>IF(B381="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B381,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B381="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B381,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D381" s="43" t="n"/>
@@ -14484,7 +14796,7 @@
       <c r="A382" s="42" t="n"/>
       <c r="B382" s="43" t="n"/>
       <c r="C382" s="5">
-        <f>IF(B382="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B382,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B382="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B382,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D382" s="43" t="n"/>
@@ -14501,7 +14813,7 @@
       <c r="A383" s="42" t="n"/>
       <c r="B383" s="43" t="n"/>
       <c r="C383" s="5">
-        <f>IF(B383="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B383,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B383="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B383,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D383" s="43" t="n"/>
@@ -14518,7 +14830,7 @@
       <c r="A384" s="42" t="n"/>
       <c r="B384" s="43" t="n"/>
       <c r="C384" s="5">
-        <f>IF(B384="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B384,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B384="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B384,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D384" s="43" t="n"/>
@@ -14535,7 +14847,7 @@
       <c r="A385" s="42" t="n"/>
       <c r="B385" s="43" t="n"/>
       <c r="C385" s="5">
-        <f>IF(B385="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B385,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B385="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B385,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D385" s="43" t="n"/>
@@ -14552,7 +14864,7 @@
       <c r="A386" s="42" t="n"/>
       <c r="B386" s="43" t="n"/>
       <c r="C386" s="5">
-        <f>IF(B386="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B386,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B386="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B386,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D386" s="43" t="n"/>
@@ -14569,7 +14881,7 @@
       <c r="A387" s="42" t="n"/>
       <c r="B387" s="43" t="n"/>
       <c r="C387" s="5">
-        <f>IF(B387="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B387,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B387="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B387,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D387" s="43" t="n"/>
@@ -14586,7 +14898,7 @@
       <c r="A388" s="42" t="n"/>
       <c r="B388" s="43" t="n"/>
       <c r="C388" s="5">
-        <f>IF(B388="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B388,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B388="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B388,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D388" s="43" t="n"/>
@@ -14603,7 +14915,7 @@
       <c r="A389" s="42" t="n"/>
       <c r="B389" s="43" t="n"/>
       <c r="C389" s="5">
-        <f>IF(B389="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B389,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B389="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B389,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D389" s="43" t="n"/>
@@ -14620,7 +14932,7 @@
       <c r="A390" s="42" t="n"/>
       <c r="B390" s="43" t="n"/>
       <c r="C390" s="5">
-        <f>IF(B390="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B390,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B390="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B390,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D390" s="43" t="n"/>
@@ -14637,7 +14949,7 @@
       <c r="A391" s="42" t="n"/>
       <c r="B391" s="43" t="n"/>
       <c r="C391" s="5">
-        <f>IF(B391="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B391,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B391="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B391,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D391" s="43" t="n"/>
@@ -14654,7 +14966,7 @@
       <c r="A392" s="42" t="n"/>
       <c r="B392" s="43" t="n"/>
       <c r="C392" s="5">
-        <f>IF(B392="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B392,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B392="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B392,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D392" s="43" t="n"/>
@@ -14671,7 +14983,7 @@
       <c r="A393" s="42" t="n"/>
       <c r="B393" s="43" t="n"/>
       <c r="C393" s="5">
-        <f>IF(B393="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B393,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B393="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B393,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D393" s="43" t="n"/>
@@ -14688,7 +15000,7 @@
       <c r="A394" s="42" t="n"/>
       <c r="B394" s="43" t="n"/>
       <c r="C394" s="5">
-        <f>IF(B394="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B394,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B394="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B394,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D394" s="43" t="n"/>
@@ -14705,7 +15017,7 @@
       <c r="A395" s="42" t="n"/>
       <c r="B395" s="43" t="n"/>
       <c r="C395" s="5">
-        <f>IF(B395="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B395,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B395="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B395,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D395" s="43" t="n"/>
@@ -14722,7 +15034,7 @@
       <c r="A396" s="42" t="n"/>
       <c r="B396" s="43" t="n"/>
       <c r="C396" s="5">
-        <f>IF(B396="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B396,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B396="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B396,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D396" s="43" t="n"/>
@@ -14739,7 +15051,7 @@
       <c r="A397" s="42" t="n"/>
       <c r="B397" s="43" t="n"/>
       <c r="C397" s="5">
-        <f>IF(B397="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B397,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B397="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B397,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D397" s="43" t="n"/>
@@ -14756,7 +15068,7 @@
       <c r="A398" s="42" t="n"/>
       <c r="B398" s="43" t="n"/>
       <c r="C398" s="5">
-        <f>IF(B398="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B398,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B398="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B398,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D398" s="43" t="n"/>
@@ -14773,7 +15085,7 @@
       <c r="A399" s="42" t="n"/>
       <c r="B399" s="43" t="n"/>
       <c r="C399" s="5">
-        <f>IF(B399="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B399,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B399="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B399,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D399" s="43" t="n"/>
@@ -14790,7 +15102,7 @@
       <c r="A400" s="42" t="n"/>
       <c r="B400" s="43" t="n"/>
       <c r="C400" s="5">
-        <f>IF(B400="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$51,MATCH(B400,'Lista de materiales'!$A$5:$A$51,0)),"ID no existe"))</f>
+        <f>IF(B400="","",IFERROR(INDEX('Lista de materiales'!$C$5:$C$54,MATCH(B400,'Lista de materiales'!$A$5:$A$54,0)),"ID no existe"))</f>
         <v/>
       </c>
       <c r="D400" s="43" t="n"/>
@@ -14809,7 +15121,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B10:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lista de materiales'!$A$5:$A$51</formula1>
+      <formula1>'Lista de materiales'!$A$5:$A$54</formula1>
     </dataValidation>
     <dataValidation sqref="G10:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Miembros</formula1>
@@ -15020,7 +15332,7 @@
         </is>
       </c>
       <c r="B9" s="50">
-        <f>IF('Lista de materiales'!$U$47="Ya lo tenemos",0,'Lista de materiales'!$T$47)</f>
+        <f>IF('Lista de materiales'!$U$50="Ya lo tenemos",0,'Lista de materiales'!$T$50)</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
